--- a/artfynd/A 33012-2024 artfynd.xlsx
+++ b/artfynd/A 33012-2024 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120391210</v>
+        <v>120391273</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>56532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,22 +824,34 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>munkedal Krokstad, Boh</t>
+          <t>Munkedal Krokstad, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>313613</v>
+        <v>313609</v>
       </c>
       <c r="R3" t="n">
-        <v>6520749</v>
+        <v>6520729</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,11 +891,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>18:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hack basen död tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,6 +901,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -910,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120391273</v>
+        <v>120391210</v>
       </c>
       <c r="B4" t="n">
-        <v>56532</v>
+        <v>57336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,25 +934,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -949,34 +961,22 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Munkedal Krokstad, Boh</t>
+          <t>munkedal Krokstad, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>313609</v>
+        <v>313613</v>
       </c>
       <c r="R4" t="n">
-        <v>6520729</v>
+        <v>6520749</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1016,6 +1016,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack basen död tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,11 +1031,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 33012-2024 artfynd.xlsx
+++ b/artfynd/A 33012-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,6 +1045,4295 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120453798</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>313302</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6521038</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120453956</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>313269</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6520997</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Troligen en hane men lite svår att exakt se när han flög förbi.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120453330</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>313727</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6520657</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120453442</v>
+      </c>
+      <c r="B8" t="n">
+        <v>94704</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>313613</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6520747</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120453323</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91192</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5454</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Hornvaxskinn</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Crustoderma corneum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>313723</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6520673</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120453313</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>313719</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6520649</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120453310</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>313673</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6520528</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120453438</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>313613</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6520747</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ett par I sitt revir med tydligen 2 av årets ungar som än så länge toleras i reviret.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120453719</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>313475</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6520948</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120454114</v>
+      </c>
+      <c r="B14" t="n">
+        <v>94433</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>313253</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6520846</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120454041</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>313277</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6520849</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120454259</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91192</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5454</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Hornvaxskinn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Crustoderma corneum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>313665</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6520570</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120453996</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91870</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>313291</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6520882</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120453471</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91192</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5454</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Hornvaxskinn</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Crustoderma corneum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>313508</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6520766</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120454233</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90600</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>313395</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6520717</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ett litet och undangömd exemplar på en av gammeltallarna</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120454251</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56532</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>313460</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6520664</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>En gammal tupp</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120454016</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>313279</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6520849</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120453982</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56532</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>313285</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6520925</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>En hona och det sågs även tidigare en hona samt även en tupp i området.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120452908</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90848</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>71</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Urskogsporing</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Neoantrodia infirma</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Renvall &amp; Niemelä) Audet</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>313704</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6520606</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Jag vet, att fyndet är mycket anmärkningsvärt i den delen av landet och jag själv kunde knappast tro det,för fyndet ligger utanför där jag själv och andra har rapporterad fynd för arten. Den brukar vanligen förekomma sparsam i norra Norrlands inland ner till norra Värmland. Men nu är det faktiskt så att Bohuslän/Dalsland har åtminstone i de norra delarna aldrig varit skogslösa som det påstås. I det trakter där fyndet gjorts finns faktiskt urskogsartad skog enligt definition  med en skoglig kontinuitet som sträcker sig åtminstone till 1680. Historisk källmaterial berättar om att även under den mest skogslösa tiden dvs. i mitten av 1800 talet om djup skogsbygd med timmerskogar i trakten. Faktum är att jag för två år sedan hade ytterligare ett fynd av urskogsporing i ett närbelägäget område som kyrkan ville hugga, då vågade jag inte att rapportera in för jag aldrig tidigare under nästan 30 år med skoglig naturvärdesinventering åt alla aktörer i landet varit med om liknande.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120453447</v>
+      </c>
+      <c r="B24" t="n">
+        <v>94433</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>313613</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6520747</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120453731</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>313412</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6521002</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120453763</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>313385</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6521062</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120453474</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>313546</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6520792</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120453741</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>313401</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6521033</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120453424</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>313613</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6520747</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120453342</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>313691</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6520712</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>En hane i sitt revir som hördes flera gånger som sedan landat på stambasen av en tall och började söka föda innan den skrämdes av mig.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120453391</v>
+      </c>
+      <c r="B31" t="n">
+        <v>94704</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>313617</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6520749</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120453531</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90804</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1102</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gäckporing</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Postia parva</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Renvall) Renvall</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>313519</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6520864</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120453858</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92048</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>313282</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6521011</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ett fint exemplar som i bilderboken på rätt substrat och i rätt miljö dvs. senvuxen och riktig gammal tallnaturskog med urskogsartad karaktär.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120453745</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57202</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100011</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kungsörn</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Aquila chrysaetos</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>313401</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6521033</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120453987</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>313285</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6520925</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120453460</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>313498</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6520773</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120453528</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>313517</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6520845</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120453698</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>313500</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6520930</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ett stationär par med två än så länge kvarvarande ungar</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120454108</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>313253</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6520846</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Tydliga hackspår</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120453481</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>313558</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6520816</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120453488</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>313547</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6520844</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120453364</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>313632</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6520770</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120453817</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>313287</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6521023</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33012-2024 artfynd.xlsx
+++ b/artfynd/A 33012-2024 artfynd.xlsx
@@ -1047,7 +1047,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120453798</v>
+        <v>120453460</v>
       </c>
       <c r="B5" t="n">
         <v>79160</v>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>313302</v>
+        <v>313498</v>
       </c>
       <c r="R5" t="n">
-        <v>6521038</v>
+        <v>6520773</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120453956</v>
+        <v>120453330</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>79160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,31 +1169,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1201,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>313269</v>
+        <v>313727</v>
       </c>
       <c r="R6" t="n">
-        <v>6520997</v>
+        <v>6520657</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1231,17 +1226,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Troligen en hane men lite svår att exakt se när han flög förbi.</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,6 +1240,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1268,7 +1259,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120453330</v>
+        <v>120453719</v>
       </c>
       <c r="B7" t="n">
         <v>79160</v>
@@ -1311,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>313727</v>
+        <v>313475</v>
       </c>
       <c r="R7" t="n">
-        <v>6520657</v>
+        <v>6520948</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,12 +1332,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120453442</v>
+        <v>120454259</v>
       </c>
       <c r="B8" t="n">
-        <v>94704</v>
+        <v>91192</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,31 +1377,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>5454</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1418,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>313613</v>
+        <v>313665</v>
       </c>
       <c r="R8" t="n">
-        <v>6520747</v>
+        <v>6520570</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1448,12 +1438,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120453323</v>
+        <v>120454041</v>
       </c>
       <c r="B9" t="n">
-        <v>91192</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,26 +1487,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5454</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1524,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>313723</v>
+        <v>313277</v>
       </c>
       <c r="R9" t="n">
-        <v>6520673</v>
+        <v>6520849</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1554,12 +1549,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,7 +1563,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1697,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120453310</v>
+        <v>120453447</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>94433</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,35 +1703,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2667</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1745,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>313673</v>
+        <v>313613</v>
       </c>
       <c r="R11" t="n">
-        <v>6520528</v>
+        <v>6520747</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1789,6 +1779,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1807,10 +1798,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120453438</v>
+        <v>120453987</v>
       </c>
       <c r="B12" t="n">
-        <v>57473</v>
+        <v>79160</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1823,35 +1814,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1859,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>313613</v>
+        <v>313285</v>
       </c>
       <c r="R12" t="n">
-        <v>6520747</v>
+        <v>6520925</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1889,17 +1871,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ett par I sitt revir med tydligen 2 av årets ungar som än så länge toleras i reviret.</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,6 +1885,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1926,7 +1904,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120453719</v>
+        <v>120453731</v>
       </c>
       <c r="B13" t="n">
         <v>79160</v>
@@ -1969,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>313475</v>
+        <v>313412</v>
       </c>
       <c r="R13" t="n">
-        <v>6520948</v>
+        <v>6521002</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2032,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120454114</v>
+        <v>120453488</v>
       </c>
       <c r="B14" t="n">
-        <v>94433</v>
+        <v>57336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,31 +2022,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2667</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2076,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>313253</v>
+        <v>313547</v>
       </c>
       <c r="R14" t="n">
-        <v>6520846</v>
+        <v>6520844</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2106,12 +2088,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,7 +2102,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2139,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120454041</v>
+        <v>120453310</v>
       </c>
       <c r="B15" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2155,16 +2136,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2177,7 +2158,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2187,10 +2168,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>313277</v>
+        <v>313673</v>
       </c>
       <c r="R15" t="n">
-        <v>6520849</v>
+        <v>6520528</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2217,12 +2198,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2249,10 +2230,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120454259</v>
+        <v>120453858</v>
       </c>
       <c r="B16" t="n">
-        <v>91192</v>
+        <v>92048</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2265,21 +2246,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5454</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2292,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>313665</v>
+        <v>313282</v>
       </c>
       <c r="R16" t="n">
-        <v>6520570</v>
+        <v>6521011</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2328,6 +2309,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ett fint exemplar som i bilderboken på rätt substrat och i rätt miljö dvs. senvuxen och riktig gammal tallnaturskog med urskogsartad karaktär.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2341,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120453996</v>
+        <v>120453391</v>
       </c>
       <c r="B17" t="n">
-        <v>91870</v>
+        <v>94704</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,26 +2357,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2398,10 +2385,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>313291</v>
+        <v>313617</v>
       </c>
       <c r="R17" t="n">
-        <v>6520882</v>
+        <v>6520749</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2428,12 +2415,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2461,10 +2448,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120453471</v>
+        <v>120453741</v>
       </c>
       <c r="B18" t="n">
-        <v>91192</v>
+        <v>79160</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2477,21 +2464,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5454</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2504,10 +2491,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>313508</v>
+        <v>313401</v>
       </c>
       <c r="R18" t="n">
-        <v>6520766</v>
+        <v>6521033</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2534,12 +2521,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2567,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120454233</v>
+        <v>120453528</v>
       </c>
       <c r="B19" t="n">
-        <v>90600</v>
+        <v>79160</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2583,21 +2570,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2610,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>313395</v>
+        <v>313517</v>
       </c>
       <c r="R19" t="n">
-        <v>6520717</v>
+        <v>6520845</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2640,17 +2627,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ett litet och undangömd exemplar på en av gammeltallarna</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2678,10 +2660,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120454251</v>
+        <v>120453698</v>
       </c>
       <c r="B20" t="n">
-        <v>56532</v>
+        <v>57473</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2690,43 +2672,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2734,10 +2712,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>313460</v>
+        <v>313500</v>
       </c>
       <c r="R20" t="n">
-        <v>6520664</v>
+        <v>6520930</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2774,7 +2752,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>En gammal tupp</t>
+          <t>Ett stationär par med två än så länge kvarvarande ungar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2801,10 +2779,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120454016</v>
+        <v>120453798</v>
       </c>
       <c r="B21" t="n">
-        <v>57336</v>
+        <v>79160</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2817,27 +2795,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2845,10 +2822,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>313279</v>
+        <v>313302</v>
       </c>
       <c r="R21" t="n">
-        <v>6520849</v>
+        <v>6521038</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2883,17 +2860,13 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2912,10 +2885,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120453982</v>
+        <v>120453531</v>
       </c>
       <c r="B22" t="n">
-        <v>56532</v>
+        <v>90804</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2924,43 +2897,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>1102</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gäckporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Postia parva</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Renvall) Renvall</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2968,10 +2928,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>313285</v>
+        <v>313519</v>
       </c>
       <c r="R22" t="n">
-        <v>6520925</v>
+        <v>6520864</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2998,17 +2958,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>En hona och det sågs även tidigare en hona samt även en tupp i området.</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3017,6 +2972,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3035,10 +2991,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120452908</v>
+        <v>120454251</v>
       </c>
       <c r="B23" t="n">
-        <v>90848</v>
+        <v>56532</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3047,30 +3003,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>71</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3078,10 +3047,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>313704</v>
+        <v>313460</v>
       </c>
       <c r="R23" t="n">
-        <v>6520606</v>
+        <v>6520664</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3108,17 +3077,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Jag vet, att fyndet är mycket anmärkningsvärt i den delen av landet och jag själv kunde knappast tro det,för fyndet ligger utanför där jag själv och andra har rapporterad fynd för arten. Den brukar vanligen förekomma sparsam i norra Norrlands inland ner till norra Värmland. Men nu är det faktiskt så att Bohuslän/Dalsland har åtminstone i de norra delarna aldrig varit skogslösa som det påstås. I det trakter där fyndet gjorts finns faktiskt urskogsartad skog enligt definition  med en skoglig kontinuitet som sträcker sig åtminstone till 1680. Historisk källmaterial berättar om att även under den mest skogslösa tiden dvs. i mitten av 1800 talet om djup skogsbygd med timmerskogar i trakten. Faktum är att jag för två år sedan hade ytterligare ett fynd av urskogsporing i ett närbelägäget område som kyrkan ville hugga, då vågade jag inte att rapportera in för jag aldrig tidigare under nästan 30 år med skoglig naturvärdesinventering åt alla aktörer i landet varit med om liknande.</t>
+          <t>En gammal tupp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3127,7 +3096,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3146,10 +3114,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120453447</v>
+        <v>120453474</v>
       </c>
       <c r="B24" t="n">
-        <v>94433</v>
+        <v>57336</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3158,31 +3126,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2667</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3190,10 +3162,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>313613</v>
+        <v>313546</v>
       </c>
       <c r="R24" t="n">
-        <v>6520747</v>
+        <v>6520792</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3234,7 +3206,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3253,10 +3224,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120453731</v>
+        <v>120453364</v>
       </c>
       <c r="B25" t="n">
-        <v>79160</v>
+        <v>91881</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3269,24 +3240,28 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3296,10 +3271,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>313412</v>
+        <v>313632</v>
       </c>
       <c r="R25" t="n">
-        <v>6521002</v>
+        <v>6520770</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3326,12 +3301,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3359,10 +3334,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120453763</v>
+        <v>120453956</v>
       </c>
       <c r="B26" t="n">
-        <v>79160</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3375,26 +3350,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3402,10 +3382,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>313385</v>
+        <v>313269</v>
       </c>
       <c r="R26" t="n">
-        <v>6521062</v>
+        <v>6520997</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3440,13 +3420,17 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Troligen en hane men lite svår att exakt se när han flög förbi.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3465,10 +3449,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120453474</v>
+        <v>120452908</v>
       </c>
       <c r="B27" t="n">
-        <v>57336</v>
+        <v>90848</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3477,35 +3461,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>71</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3513,10 +3492,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>313546</v>
+        <v>313704</v>
       </c>
       <c r="R27" t="n">
-        <v>6520792</v>
+        <v>6520606</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3551,12 +3530,18 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Jag vet, att fyndet är mycket anmärkningsvärt i den delen av landet och jag själv kunde knappast tro det,för fyndet ligger utanför där jag själv och andra har rapporterad fynd för arten. Den brukar vanligen förekomma sparsam i norra Norrlands inland ner till norra Värmland. Men nu är det faktiskt så att Bohuslän/Dalsland har åtminstone i de norra delarna aldrig varit skogslösa som det påstås. I det trakter där fyndet gjorts finns faktiskt urskogsartad skog enligt definition  med en skoglig kontinuitet som sträcker sig åtminstone till 1680. Historisk källmaterial berättar om att även under den mest skogslösa tiden dvs. i mitten av 1800 talet om djup skogsbygd med timmerskogar i trakten. Faktum är att jag för två år sedan hade ytterligare ett fynd av urskogsporing i ett närbelägäget område som kyrkan ville hugga, då vågade jag inte att rapportera in för jag aldrig tidigare under nästan 30 år med skoglig naturvärdesinventering åt alla aktörer i landet varit med om liknande.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3575,10 +3560,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120453741</v>
+        <v>120453745</v>
       </c>
       <c r="B28" t="n">
-        <v>79160</v>
+        <v>57202</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3591,26 +3576,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>100011</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3662,7 +3648,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3681,10 +3666,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120453424</v>
+        <v>120454233</v>
       </c>
       <c r="B29" t="n">
-        <v>57336</v>
+        <v>90600</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3697,31 +3682,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3729,10 +3709,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>313613</v>
+        <v>313395</v>
       </c>
       <c r="R29" t="n">
-        <v>6520747</v>
+        <v>6520717</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3759,12 +3739,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ett litet och undangömd exemplar på en av gammeltallarna</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3773,6 +3758,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3914,10 +3900,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120453391</v>
+        <v>120453481</v>
       </c>
       <c r="B31" t="n">
-        <v>94704</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3926,31 +3912,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2180</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3958,10 +3948,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>313617</v>
+        <v>313558</v>
       </c>
       <c r="R31" t="n">
-        <v>6520749</v>
+        <v>6520816</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4002,7 +3992,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4021,10 +4010,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120453531</v>
+        <v>120453996</v>
       </c>
       <c r="B32" t="n">
-        <v>90804</v>
+        <v>91870</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4033,25 +4022,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1102</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gäckporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Postia parva</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Renvall) Renvall</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4064,10 +4053,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>313519</v>
+        <v>313291</v>
       </c>
       <c r="R32" t="n">
-        <v>6520864</v>
+        <v>6520882</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4094,12 +4083,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4127,10 +4116,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120453858</v>
+        <v>120453438</v>
       </c>
       <c r="B33" t="n">
-        <v>92048</v>
+        <v>57473</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4143,26 +4132,35 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4170,10 +4168,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>313282</v>
+        <v>313613</v>
       </c>
       <c r="R33" t="n">
-        <v>6521011</v>
+        <v>6520747</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4200,17 +4198,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ett fint exemplar som i bilderboken på rätt substrat och i rätt miljö dvs. senvuxen och riktig gammal tallnaturskog med urskogsartad karaktär.</t>
+          <t>Ett par I sitt revir med tydligen 2 av årets ungar som än så länge toleras i reviret.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4219,7 +4217,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4238,10 +4235,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120453745</v>
+        <v>120454108</v>
       </c>
       <c r="B34" t="n">
-        <v>57202</v>
+        <v>57336</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4254,16 +4251,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100011</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4274,7 +4271,11 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4282,10 +4283,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>313401</v>
+        <v>313253</v>
       </c>
       <c r="R34" t="n">
-        <v>6521033</v>
+        <v>6520846</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4318,6 +4319,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Tydliga hackspår</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4344,10 +4350,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120453987</v>
+        <v>120453982</v>
       </c>
       <c r="B35" t="n">
-        <v>79160</v>
+        <v>56532</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4356,30 +4362,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4425,13 +4444,17 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>En hona och det sågs även tidigare en hona samt även en tupp i området.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4450,7 +4473,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120453460</v>
+        <v>120453763</v>
       </c>
       <c r="B36" t="n">
         <v>79160</v>
@@ -4493,10 +4516,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>313498</v>
+        <v>313385</v>
       </c>
       <c r="R36" t="n">
-        <v>6520773</v>
+        <v>6521062</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4523,12 +4546,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4556,10 +4579,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120453528</v>
+        <v>120453442</v>
       </c>
       <c r="B37" t="n">
-        <v>79160</v>
+        <v>94704</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4568,30 +4591,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4599,10 +4623,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>313517</v>
+        <v>313613</v>
       </c>
       <c r="R37" t="n">
-        <v>6520845</v>
+        <v>6520747</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4662,10 +4686,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120453698</v>
+        <v>120453323</v>
       </c>
       <c r="B38" t="n">
-        <v>57473</v>
+        <v>91192</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4678,35 +4702,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>5454</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4714,10 +4729,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>313500</v>
+        <v>313723</v>
       </c>
       <c r="R38" t="n">
-        <v>6520930</v>
+        <v>6520673</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4744,17 +4759,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ett stationär par med två än så länge kvarvarande ungar</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4763,6 +4773,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4781,10 +4792,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120454108</v>
+        <v>120453471</v>
       </c>
       <c r="B39" t="n">
-        <v>57336</v>
+        <v>91192</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4797,31 +4808,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>5454</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4829,10 +4835,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>313253</v>
+        <v>313508</v>
       </c>
       <c r="R39" t="n">
-        <v>6520846</v>
+        <v>6520766</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4859,17 +4865,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Tydliga hackspår</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4878,6 +4879,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4896,10 +4898,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120453481</v>
+        <v>120454016</v>
       </c>
       <c r="B40" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4912,16 +4914,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4932,11 +4934,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4944,10 +4942,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>313558</v>
+        <v>313279</v>
       </c>
       <c r="R40" t="n">
-        <v>6520816</v>
+        <v>6520849</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4974,12 +4972,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5006,7 +5009,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120453488</v>
+        <v>120453424</v>
       </c>
       <c r="B41" t="n">
         <v>57336</v>
@@ -5044,7 +5047,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5054,10 +5057,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>313547</v>
+        <v>313613</v>
       </c>
       <c r="R41" t="n">
-        <v>6520844</v>
+        <v>6520747</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5116,10 +5119,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120453364</v>
+        <v>120453817</v>
       </c>
       <c r="B42" t="n">
-        <v>91881</v>
+        <v>57336</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5132,30 +5135,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5163,10 +5167,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>313632</v>
+        <v>313287</v>
       </c>
       <c r="R42" t="n">
-        <v>6520770</v>
+        <v>6521023</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5193,12 +5197,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5207,7 +5211,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5226,10 +5229,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120453817</v>
+        <v>120454114</v>
       </c>
       <c r="B43" t="n">
-        <v>57336</v>
+        <v>94433</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5238,35 +5241,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>2667</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5274,10 +5273,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>313287</v>
+        <v>313253</v>
       </c>
       <c r="R43" t="n">
-        <v>6521023</v>
+        <v>6520846</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5318,6 +5317,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33012-2024 artfynd.xlsx
+++ b/artfynd/A 33012-2024 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120391273</v>
+        <v>120391210</v>
       </c>
       <c r="B3" t="n">
-        <v>56532</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,34 +824,22 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Munkedal Krokstad, Boh</t>
+          <t>munkedal Krokstad, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>313609</v>
+        <v>313613</v>
       </c>
       <c r="R3" t="n">
-        <v>6520729</v>
+        <v>6520749</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -893,6 +881,11 @@
           <t>18:00</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hack basen död tall</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,11 +894,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -922,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120391210</v>
+        <v>120391273</v>
       </c>
       <c r="B4" t="n">
-        <v>57336</v>
+        <v>56532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,25 +922,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -961,22 +949,34 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>munkedal Krokstad, Boh</t>
+          <t>Munkedal Krokstad, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>313613</v>
+        <v>313609</v>
       </c>
       <c r="R4" t="n">
-        <v>6520749</v>
+        <v>6520729</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,11 +1018,6 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack basen död tall</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1031,6 +1026,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120453460</v>
+        <v>120454041</v>
       </c>
       <c r="B5" t="n">
-        <v>79160</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,26 +1063,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1090,10 +1095,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>313498</v>
+        <v>313277</v>
       </c>
       <c r="R5" t="n">
-        <v>6520773</v>
+        <v>6520849</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1120,12 +1125,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,7 +1139,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1153,7 +1157,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120453330</v>
+        <v>120453798</v>
       </c>
       <c r="B6" t="n">
         <v>79160</v>
@@ -1196,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>313727</v>
+        <v>313302</v>
       </c>
       <c r="R6" t="n">
-        <v>6520657</v>
+        <v>6521038</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1226,12 +1230,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120453719</v>
+        <v>120453471</v>
       </c>
       <c r="B7" t="n">
-        <v>79160</v>
+        <v>91192</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,21 +1279,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>5454</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,10 +1306,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>313475</v>
+        <v>313508</v>
       </c>
       <c r="R7" t="n">
-        <v>6520948</v>
+        <v>6520766</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1332,12 +1336,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1369,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120454259</v>
+        <v>120453391</v>
       </c>
       <c r="B8" t="n">
-        <v>91192</v>
+        <v>94704</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,30 +1381,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5454</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1408,10 +1413,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>313665</v>
+        <v>313617</v>
       </c>
       <c r="R8" t="n">
-        <v>6520570</v>
+        <v>6520749</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,12 +1443,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120454041</v>
+        <v>120454233</v>
       </c>
       <c r="B9" t="n">
-        <v>57336</v>
+        <v>90600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,31 +1492,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>313277</v>
+        <v>313395</v>
       </c>
       <c r="R9" t="n">
-        <v>6520849</v>
+        <v>6520717</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1557,12 +1557,18 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ett litet och undangömd exemplar på en av gammeltallarna</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1581,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120453313</v>
+        <v>120453438</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,29 +1603,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1629,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>313719</v>
+        <v>313613</v>
       </c>
       <c r="R10" t="n">
-        <v>6520649</v>
+        <v>6520747</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1665,6 +1675,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ett par I sitt revir med tydligen 2 av årets ungar som än så länge toleras i reviret.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120453447</v>
+        <v>120453719</v>
       </c>
       <c r="B11" t="n">
-        <v>94433</v>
+        <v>79160</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,31 +1718,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2667</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1735,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>313613</v>
+        <v>313475</v>
       </c>
       <c r="R11" t="n">
-        <v>6520747</v>
+        <v>6520948</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1765,12 +1779,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,10 +1812,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120453987</v>
+        <v>120454016</v>
       </c>
       <c r="B12" t="n">
-        <v>79160</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1814,26 +1828,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1841,10 +1856,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>313285</v>
+        <v>313279</v>
       </c>
       <c r="R12" t="n">
-        <v>6520925</v>
+        <v>6520849</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1879,13 +1894,17 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1904,10 +1923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120453731</v>
+        <v>120454108</v>
       </c>
       <c r="B13" t="n">
-        <v>79160</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1920,26 +1939,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1947,10 +1971,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>313412</v>
+        <v>313253</v>
       </c>
       <c r="R13" t="n">
-        <v>6521002</v>
+        <v>6520846</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1985,13 +2009,17 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Tydliga hackspår</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2010,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120453488</v>
+        <v>120453763</v>
       </c>
       <c r="B14" t="n">
-        <v>57336</v>
+        <v>79160</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2026,31 +2054,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2058,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>313547</v>
+        <v>313385</v>
       </c>
       <c r="R14" t="n">
-        <v>6520844</v>
+        <v>6521062</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2088,12 +2111,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2102,6 +2125,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2120,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120453310</v>
+        <v>120453460</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>79160</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2136,31 +2160,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2168,10 +2187,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>313673</v>
+        <v>313498</v>
       </c>
       <c r="R15" t="n">
-        <v>6520528</v>
+        <v>6520773</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2212,6 +2231,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2230,10 +2250,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120453858</v>
+        <v>120453698</v>
       </c>
       <c r="B16" t="n">
-        <v>92048</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2246,26 +2266,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2273,10 +2302,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>313282</v>
+        <v>313500</v>
       </c>
       <c r="R16" t="n">
-        <v>6521011</v>
+        <v>6520930</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2313,7 +2342,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ett fint exemplar som i bilderboken på rätt substrat och i rätt miljö dvs. senvuxen och riktig gammal tallnaturskog med urskogsartad karaktär.</t>
+          <t>Ett stationär par med två än så länge kvarvarande ungar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2322,7 +2351,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2341,10 +2369,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120453391</v>
+        <v>120453481</v>
       </c>
       <c r="B17" t="n">
-        <v>94704</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2353,31 +2381,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2385,10 +2417,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>313617</v>
+        <v>313558</v>
       </c>
       <c r="R17" t="n">
-        <v>6520749</v>
+        <v>6520816</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2429,7 +2461,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2448,10 +2479,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120453741</v>
+        <v>120454259</v>
       </c>
       <c r="B18" t="n">
-        <v>79160</v>
+        <v>91192</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2464,21 +2495,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>5454</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2491,10 +2522,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>313401</v>
+        <v>313665</v>
       </c>
       <c r="R18" t="n">
-        <v>6521033</v>
+        <v>6520570</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2554,10 +2585,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120453528</v>
+        <v>120453442</v>
       </c>
       <c r="B19" t="n">
-        <v>79160</v>
+        <v>94704</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2566,30 +2597,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2597,10 +2629,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>313517</v>
+        <v>313613</v>
       </c>
       <c r="R19" t="n">
-        <v>6520845</v>
+        <v>6520747</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2660,10 +2692,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120453698</v>
+        <v>120454114</v>
       </c>
       <c r="B20" t="n">
-        <v>57473</v>
+        <v>94433</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2672,39 +2704,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>2667</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2712,10 +2736,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>313500</v>
+        <v>313253</v>
       </c>
       <c r="R20" t="n">
-        <v>6520930</v>
+        <v>6520846</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2750,17 +2774,13 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ett stationär par med två än så länge kvarvarande ungar</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2779,10 +2799,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120453798</v>
+        <v>120453342</v>
       </c>
       <c r="B21" t="n">
-        <v>79160</v>
+        <v>57336</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2795,26 +2815,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2822,10 +2855,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>313302</v>
+        <v>313691</v>
       </c>
       <c r="R21" t="n">
-        <v>6521038</v>
+        <v>6520712</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2852,12 +2885,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>En hane i sitt revir som hördes flera gånger som sedan landat på stambasen av en tall och började söka föda innan den skrämdes av mig.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2866,7 +2904,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2885,10 +2922,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120453531</v>
+        <v>120453424</v>
       </c>
       <c r="B22" t="n">
-        <v>90804</v>
+        <v>57336</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2901,26 +2938,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1102</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gäckporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Postia parva</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Renvall) Renvall</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2928,10 +2970,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>313519</v>
+        <v>313613</v>
       </c>
       <c r="R22" t="n">
-        <v>6520864</v>
+        <v>6520747</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2972,7 +3014,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2991,10 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120454251</v>
+        <v>120453817</v>
       </c>
       <c r="B23" t="n">
-        <v>56532</v>
+        <v>57336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3003,43 +3044,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3047,10 +3080,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>313460</v>
+        <v>313287</v>
       </c>
       <c r="R23" t="n">
-        <v>6520664</v>
+        <v>6521023</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3083,11 +3116,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>En gammal tupp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3114,10 +3142,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120453474</v>
+        <v>120454251</v>
       </c>
       <c r="B24" t="n">
-        <v>57336</v>
+        <v>56532</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3126,35 +3154,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3162,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>313546</v>
+        <v>313460</v>
       </c>
       <c r="R24" t="n">
-        <v>6520792</v>
+        <v>6520664</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3192,12 +3228,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>En gammal tupp</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3224,10 +3265,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120453364</v>
+        <v>120453956</v>
       </c>
       <c r="B25" t="n">
-        <v>91881</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3240,30 +3281,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3271,10 +3313,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>313632</v>
+        <v>313269</v>
       </c>
       <c r="R25" t="n">
-        <v>6520770</v>
+        <v>6520997</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3301,12 +3343,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Troligen en hane men lite svår att exakt se när han flög förbi.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3315,7 +3362,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3334,10 +3380,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120453956</v>
+        <v>120453987</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>79160</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3350,31 +3396,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3382,10 +3423,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>313269</v>
+        <v>313285</v>
       </c>
       <c r="R26" t="n">
-        <v>6520997</v>
+        <v>6520925</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3420,17 +3461,13 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Troligen en hane men lite svår att exakt se när han flög förbi.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3449,10 +3486,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120452908</v>
+        <v>120453858</v>
       </c>
       <c r="B27" t="n">
-        <v>90848</v>
+        <v>92048</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3461,25 +3498,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>71</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3492,10 +3529,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>313704</v>
+        <v>313282</v>
       </c>
       <c r="R27" t="n">
-        <v>6520606</v>
+        <v>6521011</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3522,17 +3559,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Jag vet, att fyndet är mycket anmärkningsvärt i den delen av landet och jag själv kunde knappast tro det,för fyndet ligger utanför där jag själv och andra har rapporterad fynd för arten. Den brukar vanligen förekomma sparsam i norra Norrlands inland ner till norra Värmland. Men nu är det faktiskt så att Bohuslän/Dalsland har åtminstone i de norra delarna aldrig varit skogslösa som det påstås. I det trakter där fyndet gjorts finns faktiskt urskogsartad skog enligt definition  med en skoglig kontinuitet som sträcker sig åtminstone till 1680. Historisk källmaterial berättar om att även under den mest skogslösa tiden dvs. i mitten av 1800 talet om djup skogsbygd med timmerskogar i trakten. Faktum är att jag för två år sedan hade ytterligare ett fynd av urskogsporing i ett närbelägäget område som kyrkan ville hugga, då vågade jag inte att rapportera in för jag aldrig tidigare under nästan 30 år med skoglig naturvärdesinventering åt alla aktörer i landet varit med om liknande.</t>
+          <t>Ett fint exemplar som i bilderboken på rätt substrat och i rätt miljö dvs. senvuxen och riktig gammal tallnaturskog med urskogsartad karaktär.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3560,10 +3597,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120453745</v>
+        <v>120453330</v>
       </c>
       <c r="B28" t="n">
-        <v>57202</v>
+        <v>79160</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3576,27 +3613,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100011</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3604,10 +3640,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>313401</v>
+        <v>313727</v>
       </c>
       <c r="R28" t="n">
-        <v>6521033</v>
+        <v>6520657</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3634,12 +3670,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3648,6 +3684,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3666,10 +3703,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120454233</v>
+        <v>120453364</v>
       </c>
       <c r="B29" t="n">
-        <v>90600</v>
+        <v>91881</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3682,24 +3719,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3709,10 +3750,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>313395</v>
+        <v>313632</v>
       </c>
       <c r="R29" t="n">
-        <v>6520717</v>
+        <v>6520770</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3739,17 +3780,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ett litet och undangömd exemplar på en av gammeltallarna</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3777,10 +3813,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120453342</v>
+        <v>120453310</v>
       </c>
       <c r="B30" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3793,16 +3829,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3810,20 +3846,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3833,10 +3861,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>313691</v>
+        <v>313673</v>
       </c>
       <c r="R30" t="n">
-        <v>6520712</v>
+        <v>6520528</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3869,11 +3897,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-14</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>En hane i sitt revir som hördes flera gånger som sedan landat på stambasen av en tall och började söka föda innan den skrämdes av mig.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3900,7 +3923,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120453481</v>
+        <v>120453313</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3948,10 +3971,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>313558</v>
+        <v>313719</v>
       </c>
       <c r="R31" t="n">
-        <v>6520816</v>
+        <v>6520649</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4010,10 +4033,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120453996</v>
+        <v>120453731</v>
       </c>
       <c r="B32" t="n">
-        <v>91870</v>
+        <v>79160</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4022,25 +4045,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4053,10 +4076,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>313291</v>
+        <v>313412</v>
       </c>
       <c r="R32" t="n">
-        <v>6520882</v>
+        <v>6521002</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4116,10 +4139,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120453438</v>
+        <v>120453745</v>
       </c>
       <c r="B33" t="n">
-        <v>57473</v>
+        <v>57202</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4132,35 +4155,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100011</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4168,10 +4183,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>313613</v>
+        <v>313401</v>
       </c>
       <c r="R33" t="n">
-        <v>6520747</v>
+        <v>6521033</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4198,17 +4213,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ett par I sitt revir med tydligen 2 av årets ungar som än så länge toleras i reviret.</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4235,10 +4245,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120454108</v>
+        <v>120453447</v>
       </c>
       <c r="B34" t="n">
-        <v>57336</v>
+        <v>94433</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4247,35 +4257,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>2667</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4283,10 +4289,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>313253</v>
+        <v>313613</v>
       </c>
       <c r="R34" t="n">
-        <v>6520846</v>
+        <v>6520747</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4313,17 +4319,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Tydliga hackspår</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4332,6 +4333,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4350,10 +4352,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120453982</v>
+        <v>120453323</v>
       </c>
       <c r="B35" t="n">
-        <v>56532</v>
+        <v>91192</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4362,43 +4364,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>5454</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4406,10 +4395,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>313285</v>
+        <v>313723</v>
       </c>
       <c r="R35" t="n">
-        <v>6520925</v>
+        <v>6520673</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4436,17 +4425,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>En hona och det sågs även tidigare en hona samt även en tupp i området.</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4455,6 +4439,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4473,10 +4458,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120453763</v>
+        <v>120452908</v>
       </c>
       <c r="B36" t="n">
-        <v>79160</v>
+        <v>90848</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4485,25 +4470,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4516,10 +4501,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>313385</v>
+        <v>313704</v>
       </c>
       <c r="R36" t="n">
-        <v>6521062</v>
+        <v>6520606</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4546,12 +4531,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Jag vet, att fyndet är mycket anmärkningsvärt i den delen av landet och jag själv kunde knappast tro det,för fyndet ligger utanför där jag själv och andra har rapporterad fynd för arten. Den brukar vanligen förekomma sparsam i norra Norrlands inland ner till norra Värmland. Men nu är det faktiskt så att Bohuslän/Dalsland har åtminstone i de norra delarna aldrig varit skogslösa som det påstås. I det trakter där fyndet gjorts finns faktiskt urskogsartad skog enligt definition  med en skoglig kontinuitet som sträcker sig åtminstone till 1680. Historisk källmaterial berättar om att även under den mest skogslösa tiden dvs. i mitten av 1800 talet om djup skogsbygd med timmerskogar i trakten. Faktum är att jag för två år sedan hade ytterligare ett fynd av urskogsporing i ett närbelägäget område som kyrkan ville hugga, då vågade jag inte att rapportera in för jag aldrig tidigare under nästan 30 år med skoglig naturvärdesinventering åt alla aktörer i landet varit med om liknande.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4579,10 +4569,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120453442</v>
+        <v>120453982</v>
       </c>
       <c r="B37" t="n">
-        <v>94704</v>
+        <v>56532</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4595,27 +4585,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4623,10 +4625,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>313613</v>
+        <v>313285</v>
       </c>
       <c r="R37" t="n">
-        <v>6520747</v>
+        <v>6520925</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4653,12 +4655,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>En hona och det sågs även tidigare en hona samt även en tupp i området.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,7 +4674,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4686,10 +4692,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120453323</v>
+        <v>120453996</v>
       </c>
       <c r="B38" t="n">
-        <v>91192</v>
+        <v>91870</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4698,25 +4704,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5454</v>
+        <v>4366</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4729,10 +4735,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>313723</v>
+        <v>313291</v>
       </c>
       <c r="R38" t="n">
-        <v>6520673</v>
+        <v>6520882</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4759,12 +4765,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4792,10 +4798,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120453471</v>
+        <v>120453528</v>
       </c>
       <c r="B39" t="n">
-        <v>91192</v>
+        <v>79160</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4808,21 +4814,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5454</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4835,10 +4841,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>313508</v>
+        <v>313517</v>
       </c>
       <c r="R39" t="n">
-        <v>6520766</v>
+        <v>6520845</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4898,7 +4904,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120454016</v>
+        <v>120453488</v>
       </c>
       <c r="B40" t="n">
         <v>57336</v>
@@ -4934,7 +4940,11 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4942,10 +4952,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>313279</v>
+        <v>313547</v>
       </c>
       <c r="R40" t="n">
-        <v>6520849</v>
+        <v>6520844</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4972,17 +4982,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5009,7 +5014,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120453424</v>
+        <v>120453474</v>
       </c>
       <c r="B41" t="n">
         <v>57336</v>
@@ -5047,7 +5052,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5057,10 +5062,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>313613</v>
+        <v>313546</v>
       </c>
       <c r="R41" t="n">
-        <v>6520747</v>
+        <v>6520792</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5119,10 +5124,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120453817</v>
+        <v>120453741</v>
       </c>
       <c r="B42" t="n">
-        <v>57336</v>
+        <v>79160</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5135,31 +5140,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>313287</v>
+        <v>313401</v>
       </c>
       <c r="R42" t="n">
-        <v>6521023</v>
+        <v>6521033</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5211,6 +5211,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5229,10 +5230,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120454114</v>
+        <v>120453531</v>
       </c>
       <c r="B43" t="n">
-        <v>94433</v>
+        <v>90804</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5241,31 +5242,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2667</v>
+        <v>1102</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gäckporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Postia parva</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Renvall) Renvall</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>313253</v>
+        <v>313519</v>
       </c>
       <c r="R43" t="n">
-        <v>6520846</v>
+        <v>6520864</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5303,12 +5303,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 33012-2024 artfynd.xlsx
+++ b/artfynd/A 33012-2024 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120391210</v>
+        <v>120391273</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>56532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,22 +824,34 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>munkedal Krokstad, Boh</t>
+          <t>Munkedal Krokstad, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>313613</v>
+        <v>313609</v>
       </c>
       <c r="R3" t="n">
-        <v>6520749</v>
+        <v>6520729</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,11 +893,6 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hack basen död tall</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -894,6 +901,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -910,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120391273</v>
+        <v>120391210</v>
       </c>
       <c r="B4" t="n">
-        <v>56532</v>
+        <v>57336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,25 +934,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -949,34 +961,22 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Munkedal Krokstad, Boh</t>
+          <t>munkedal Krokstad, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>313609</v>
+        <v>313613</v>
       </c>
       <c r="R4" t="n">
-        <v>6520729</v>
+        <v>6520749</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,6 +1018,11 @@
           <t>18:00</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack basen död tall</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1026,11 +1031,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120454041</v>
+        <v>120453460</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>79160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,31 +1063,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1095,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>313277</v>
+        <v>313498</v>
       </c>
       <c r="R5" t="n">
-        <v>6520849</v>
+        <v>6520773</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1125,12 +1120,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,6 +1134,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1157,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120453798</v>
+        <v>120453858</v>
       </c>
       <c r="B6" t="n">
-        <v>79160</v>
+        <v>92048</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,21 +1169,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1200,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>313302</v>
+        <v>313282</v>
       </c>
       <c r="R6" t="n">
-        <v>6521038</v>
+        <v>6521011</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1236,6 +1232,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ett fint exemplar som i bilderboken på rätt substrat och i rätt miljö dvs. senvuxen och riktig gammal tallnaturskog med urskogsartad karaktär.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120453471</v>
+        <v>120453364</v>
       </c>
       <c r="B7" t="n">
-        <v>91192</v>
+        <v>91881</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,24 +1280,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5454</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1306,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>313508</v>
+        <v>313632</v>
       </c>
       <c r="R7" t="n">
-        <v>6520766</v>
+        <v>6520770</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1369,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120453391</v>
+        <v>120453528</v>
       </c>
       <c r="B8" t="n">
-        <v>94704</v>
+        <v>79160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,31 +1386,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1413,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>313617</v>
+        <v>313517</v>
       </c>
       <c r="R8" t="n">
-        <v>6520749</v>
+        <v>6520845</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1476,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120454233</v>
+        <v>120453741</v>
       </c>
       <c r="B9" t="n">
-        <v>90600</v>
+        <v>79160</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,21 +1496,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>313395</v>
+        <v>313401</v>
       </c>
       <c r="R9" t="n">
-        <v>6520717</v>
+        <v>6521033</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1555,11 +1559,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ett litet och undangömd exemplar på en av gammeltallarna</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120453438</v>
+        <v>120453745</v>
       </c>
       <c r="B10" t="n">
-        <v>57473</v>
+        <v>57202</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,35 +1602,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100011</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1639,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>313613</v>
+        <v>313401</v>
       </c>
       <c r="R10" t="n">
-        <v>6520747</v>
+        <v>6521033</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1669,17 +1660,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ett par I sitt revir med tydligen 2 av årets ungar som än så länge toleras i reviret.</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120453719</v>
+        <v>120453982</v>
       </c>
       <c r="B11" t="n">
-        <v>79160</v>
+        <v>56532</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,30 +1704,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1749,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>313475</v>
+        <v>313285</v>
       </c>
       <c r="R11" t="n">
-        <v>6520948</v>
+        <v>6520925</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1787,13 +1786,17 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>En hona och det sågs även tidigare en hona samt även en tupp i området.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1812,7 +1815,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120454016</v>
+        <v>120454041</v>
       </c>
       <c r="B12" t="n">
         <v>57336</v>
@@ -1848,7 +1851,11 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1856,7 +1863,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>313279</v>
+        <v>313277</v>
       </c>
       <c r="R12" t="n">
         <v>6520849</v>
@@ -1892,11 +1899,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120454108</v>
+        <v>120454259</v>
       </c>
       <c r="B13" t="n">
-        <v>57336</v>
+        <v>91192</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,31 +1941,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5454</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1971,10 +1968,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>313253</v>
+        <v>313665</v>
       </c>
       <c r="R13" t="n">
-        <v>6520846</v>
+        <v>6520570</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2009,17 +2006,13 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Tydliga hackspår</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2038,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120453763</v>
+        <v>120453956</v>
       </c>
       <c r="B14" t="n">
-        <v>79160</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,26 +2047,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2081,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>313385</v>
+        <v>313269</v>
       </c>
       <c r="R14" t="n">
-        <v>6521062</v>
+        <v>6520997</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2119,13 +2117,17 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Troligen en hane men lite svår att exakt se när han flög förbi.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2144,7 +2146,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120453460</v>
+        <v>120453731</v>
       </c>
       <c r="B15" t="n">
         <v>79160</v>
@@ -2187,10 +2189,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>313498</v>
+        <v>313412</v>
       </c>
       <c r="R15" t="n">
-        <v>6520773</v>
+        <v>6521002</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2217,12 +2219,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2250,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120453698</v>
+        <v>120453391</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
+        <v>94704</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2262,39 +2264,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2302,10 +2296,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>313500</v>
+        <v>313617</v>
       </c>
       <c r="R16" t="n">
-        <v>6520930</v>
+        <v>6520749</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2332,17 +2326,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ett stationär par med två än så länge kvarvarande ungar</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2351,6 +2340,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2369,7 +2359,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120453481</v>
+        <v>120453310</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2407,7 +2397,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2417,10 +2407,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>313558</v>
+        <v>313673</v>
       </c>
       <c r="R17" t="n">
-        <v>6520816</v>
+        <v>6520528</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2479,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120454259</v>
+        <v>120453424</v>
       </c>
       <c r="B18" t="n">
-        <v>91192</v>
+        <v>57336</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2495,26 +2485,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5454</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2522,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>313665</v>
+        <v>313613</v>
       </c>
       <c r="R18" t="n">
-        <v>6520570</v>
+        <v>6520747</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2552,12 +2547,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2566,7 +2561,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2585,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120453442</v>
+        <v>120454114</v>
       </c>
       <c r="B19" t="n">
-        <v>94704</v>
+        <v>94433</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2601,21 +2595,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>2667</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2629,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>313613</v>
+        <v>313253</v>
       </c>
       <c r="R19" t="n">
-        <v>6520747</v>
+        <v>6520846</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2659,12 +2653,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2692,10 +2686,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120454114</v>
+        <v>120453323</v>
       </c>
       <c r="B20" t="n">
-        <v>94433</v>
+        <v>91192</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2704,31 +2698,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2667</v>
+        <v>5454</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2736,10 +2729,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>313253</v>
+        <v>313723</v>
       </c>
       <c r="R20" t="n">
-        <v>6520846</v>
+        <v>6520673</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2766,12 +2759,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2799,10 +2792,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120453342</v>
+        <v>120453330</v>
       </c>
       <c r="B21" t="n">
-        <v>57336</v>
+        <v>79160</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,39 +2808,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2855,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>313691</v>
+        <v>313727</v>
       </c>
       <c r="R21" t="n">
-        <v>6520712</v>
+        <v>6520657</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2893,17 +2873,13 @@
           <t>2024-10-14</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>En hane i sitt revir som hördes flera gånger som sedan landat på stambasen av en tall och började söka föda innan den skrämdes av mig.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2922,10 +2898,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120453424</v>
+        <v>120453698</v>
       </c>
       <c r="B22" t="n">
-        <v>57336</v>
+        <v>57473</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2938,29 +2914,33 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2970,10 +2950,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>313613</v>
+        <v>313500</v>
       </c>
       <c r="R22" t="n">
-        <v>6520747</v>
+        <v>6520930</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3000,12 +2980,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ett stationär par med två än så länge kvarvarande ungar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3032,10 +3017,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120453817</v>
+        <v>120453798</v>
       </c>
       <c r="B23" t="n">
-        <v>57336</v>
+        <v>79160</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3048,31 +3033,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3080,10 +3060,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>313287</v>
+        <v>313302</v>
       </c>
       <c r="R23" t="n">
-        <v>6521023</v>
+        <v>6521038</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3124,6 +3104,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3142,10 +3123,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120454251</v>
+        <v>120453488</v>
       </c>
       <c r="B24" t="n">
-        <v>56532</v>
+        <v>57336</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3154,43 +3135,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3198,10 +3171,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>313460</v>
+        <v>313547</v>
       </c>
       <c r="R24" t="n">
-        <v>6520664</v>
+        <v>6520844</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3228,17 +3201,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>En gammal tupp</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3265,7 +3233,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120453956</v>
+        <v>120453313</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3303,7 +3271,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3313,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>313269</v>
+        <v>313719</v>
       </c>
       <c r="R25" t="n">
-        <v>6520997</v>
+        <v>6520649</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3343,17 +3311,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Troligen en hane men lite svår att exakt se när han flög förbi.</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3380,10 +3343,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120453987</v>
+        <v>120453474</v>
       </c>
       <c r="B26" t="n">
-        <v>79160</v>
+        <v>57336</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3396,26 +3359,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3423,10 +3391,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>313285</v>
+        <v>313546</v>
       </c>
       <c r="R26" t="n">
-        <v>6520925</v>
+        <v>6520792</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3453,12 +3421,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3467,7 +3435,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3486,10 +3453,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120453858</v>
+        <v>120453442</v>
       </c>
       <c r="B27" t="n">
-        <v>92048</v>
+        <v>94704</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3498,30 +3465,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3529,10 +3497,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>313282</v>
+        <v>313613</v>
       </c>
       <c r="R27" t="n">
-        <v>6521011</v>
+        <v>6520747</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3559,17 +3527,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ett fint exemplar som i bilderboken på rätt substrat och i rätt miljö dvs. senvuxen och riktig gammal tallnaturskog med urskogsartad karaktär.</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3597,10 +3560,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120453330</v>
+        <v>120453531</v>
       </c>
       <c r="B28" t="n">
-        <v>79160</v>
+        <v>90804</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3613,21 +3576,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>1102</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gäckporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Postia parva</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall) Renvall</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3640,10 +3603,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>313727</v>
+        <v>313519</v>
       </c>
       <c r="R28" t="n">
-        <v>6520657</v>
+        <v>6520864</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3703,10 +3666,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120453364</v>
+        <v>120453763</v>
       </c>
       <c r="B29" t="n">
-        <v>91881</v>
+        <v>79160</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3719,28 +3682,24 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3750,10 +3709,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>313632</v>
+        <v>313385</v>
       </c>
       <c r="R29" t="n">
-        <v>6520770</v>
+        <v>6521062</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3780,12 +3739,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3813,10 +3772,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120453310</v>
+        <v>120453987</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>79160</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3829,31 +3788,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3861,10 +3815,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>313673</v>
+        <v>313285</v>
       </c>
       <c r="R30" t="n">
-        <v>6520528</v>
+        <v>6520925</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3891,12 +3845,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3905,6 +3859,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3923,10 +3878,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120453313</v>
+        <v>120454233</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>90600</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3939,31 +3894,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3971,10 +3921,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>313719</v>
+        <v>313395</v>
       </c>
       <c r="R31" t="n">
-        <v>6520649</v>
+        <v>6520717</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4001,12 +3951,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ett litet och undangömd exemplar på en av gammeltallarna</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4015,6 +3970,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4033,10 +3989,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120453731</v>
+        <v>120453342</v>
       </c>
       <c r="B32" t="n">
-        <v>79160</v>
+        <v>57336</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4049,26 +4005,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4076,10 +4045,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>313412</v>
+        <v>313691</v>
       </c>
       <c r="R32" t="n">
-        <v>6521002</v>
+        <v>6520712</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4106,12 +4075,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>En hane i sitt revir som hördes flera gånger som sedan landat på stambasen av en tall och började söka föda innan den skrämdes av mig.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4120,7 +4094,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4139,10 +4112,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120453745</v>
+        <v>120453447</v>
       </c>
       <c r="B33" t="n">
-        <v>57202</v>
+        <v>94433</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4151,31 +4124,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100011</v>
+        <v>2667</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4183,10 +4156,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>313401</v>
+        <v>313613</v>
       </c>
       <c r="R33" t="n">
-        <v>6521033</v>
+        <v>6520747</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4213,12 +4186,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4227,6 +4200,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4245,10 +4219,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120453447</v>
+        <v>120453817</v>
       </c>
       <c r="B34" t="n">
-        <v>94433</v>
+        <v>57336</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4257,31 +4231,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2667</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4289,10 +4267,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>313613</v>
+        <v>313287</v>
       </c>
       <c r="R34" t="n">
-        <v>6520747</v>
+        <v>6521023</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4319,12 +4297,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4333,7 +4311,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4352,10 +4329,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120453323</v>
+        <v>120454016</v>
       </c>
       <c r="B35" t="n">
-        <v>91192</v>
+        <v>57336</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4368,26 +4345,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5454</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4395,10 +4373,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>313723</v>
+        <v>313279</v>
       </c>
       <c r="R35" t="n">
-        <v>6520673</v>
+        <v>6520849</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4425,12 +4403,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4439,7 +4422,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4458,10 +4440,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120452908</v>
+        <v>120453471</v>
       </c>
       <c r="B36" t="n">
-        <v>90848</v>
+        <v>91192</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4470,25 +4452,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>71</v>
+        <v>5454</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4501,10 +4483,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>313704</v>
+        <v>313508</v>
       </c>
       <c r="R36" t="n">
-        <v>6520606</v>
+        <v>6520766</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4537,11 +4519,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-14</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Jag vet, att fyndet är mycket anmärkningsvärt i den delen av landet och jag själv kunde knappast tro det,för fyndet ligger utanför där jag själv och andra har rapporterad fynd för arten. Den brukar vanligen förekomma sparsam i norra Norrlands inland ner till norra Värmland. Men nu är det faktiskt så att Bohuslän/Dalsland har åtminstone i de norra delarna aldrig varit skogslösa som det påstås. I det trakter där fyndet gjorts finns faktiskt urskogsartad skog enligt definition  med en skoglig kontinuitet som sträcker sig åtminstone till 1680. Historisk källmaterial berättar om att även under den mest skogslösa tiden dvs. i mitten av 1800 talet om djup skogsbygd med timmerskogar i trakten. Faktum är att jag för två år sedan hade ytterligare ett fynd av urskogsporing i ett närbelägäget område som kyrkan ville hugga, då vågade jag inte att rapportera in för jag aldrig tidigare under nästan 30 år med skoglig naturvärdesinventering åt alla aktörer i landet varit med om liknande.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4569,10 +4546,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120453982</v>
+        <v>120452908</v>
       </c>
       <c r="B37" t="n">
-        <v>56532</v>
+        <v>90848</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4581,43 +4558,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>71</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Renvall &amp; Niemelä) Audet</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4625,10 +4589,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>313285</v>
+        <v>313704</v>
       </c>
       <c r="R37" t="n">
-        <v>6520925</v>
+        <v>6520606</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4655,17 +4619,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>En hona och det sågs även tidigare en hona samt även en tupp i området.</t>
+          <t>Jag vet, att fyndet är mycket anmärkningsvärt i den delen av landet och jag själv kunde knappast tro det,för fyndet ligger utanför där jag själv och andra har rapporterad fynd för arten. Den brukar vanligen förekomma sparsam i norra Norrlands inland ner till norra Värmland. Men nu är det faktiskt så att Bohuslän/Dalsland har åtminstone i de norra delarna aldrig varit skogslösa som det påstås. I det trakter där fyndet gjorts finns faktiskt urskogsartad skog enligt definition  med en skoglig kontinuitet som sträcker sig åtminstone till 1680. Historisk källmaterial berättar om att även under den mest skogslösa tiden dvs. i mitten av 1800 talet om djup skogsbygd med timmerskogar i trakten. Faktum är att jag för två år sedan hade ytterligare ett fynd av urskogsporing i ett närbelägäget område som kyrkan ville hugga, då vågade jag inte att rapportera in för jag aldrig tidigare under nästan 30 år med skoglig naturvärdesinventering åt alla aktörer i landet varit med om liknande.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4674,6 +4638,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4692,10 +4657,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120453996</v>
+        <v>120454108</v>
       </c>
       <c r="B38" t="n">
-        <v>91870</v>
+        <v>57336</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4704,30 +4669,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4735,10 +4705,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>313291</v>
+        <v>313253</v>
       </c>
       <c r="R38" t="n">
-        <v>6520882</v>
+        <v>6520846</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4773,13 +4743,17 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Tydliga hackspår</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4798,10 +4772,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120453528</v>
+        <v>120453438</v>
       </c>
       <c r="B39" t="n">
-        <v>79160</v>
+        <v>57473</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4814,26 +4788,35 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4841,10 +4824,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>313517</v>
+        <v>313613</v>
       </c>
       <c r="R39" t="n">
-        <v>6520845</v>
+        <v>6520747</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4879,13 +4862,17 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ett par I sitt revir med tydligen 2 av årets ungar som än så länge toleras i reviret.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4904,10 +4891,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120453488</v>
+        <v>120453996</v>
       </c>
       <c r="B40" t="n">
-        <v>57336</v>
+        <v>91870</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4916,35 +4903,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>4366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4952,10 +4934,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>313547</v>
+        <v>313291</v>
       </c>
       <c r="R40" t="n">
-        <v>6520844</v>
+        <v>6520882</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4982,12 +4964,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4996,6 +4978,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5014,10 +4997,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120453474</v>
+        <v>120453481</v>
       </c>
       <c r="B41" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5030,16 +5013,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5052,7 +5035,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5062,10 +5045,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>313546</v>
+        <v>313558</v>
       </c>
       <c r="R41" t="n">
-        <v>6520792</v>
+        <v>6520816</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5124,7 +5107,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120453741</v>
+        <v>120453719</v>
       </c>
       <c r="B42" t="n">
         <v>79160</v>
@@ -5167,10 +5150,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>313401</v>
+        <v>313475</v>
       </c>
       <c r="R42" t="n">
-        <v>6521033</v>
+        <v>6520948</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5230,10 +5213,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120453531</v>
+        <v>120454251</v>
       </c>
       <c r="B43" t="n">
-        <v>90804</v>
+        <v>56532</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5242,30 +5225,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1102</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gäckporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Postia parva</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Renvall) Renvall</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5273,10 +5269,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>313519</v>
+        <v>313460</v>
       </c>
       <c r="R43" t="n">
-        <v>6520864</v>
+        <v>6520664</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5303,12 +5299,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>En gammal tupp</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5317,7 +5318,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33012-2024 artfynd.xlsx
+++ b/artfynd/A 33012-2024 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120391273</v>
+        <v>120391210</v>
       </c>
       <c r="B3" t="n">
-        <v>56532</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,34 +824,22 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Munkedal Krokstad, Boh</t>
+          <t>munkedal Krokstad, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>313609</v>
+        <v>313613</v>
       </c>
       <c r="R3" t="n">
-        <v>6520729</v>
+        <v>6520749</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -893,6 +881,11 @@
           <t>18:00</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hack basen död tall</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,11 +894,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -922,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120391210</v>
+        <v>120391273</v>
       </c>
       <c r="B4" t="n">
-        <v>57336</v>
+        <v>56532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,25 +922,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -961,22 +949,34 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>munkedal Krokstad, Boh</t>
+          <t>Munkedal Krokstad, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>313613</v>
+        <v>313609</v>
       </c>
       <c r="R4" t="n">
-        <v>6520749</v>
+        <v>6520729</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,11 +1018,6 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack basen död tall</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1031,6 +1026,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120453460</v>
+        <v>120453342</v>
       </c>
       <c r="B5" t="n">
-        <v>79160</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,26 +1063,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1090,10 +1103,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>313498</v>
+        <v>313691</v>
       </c>
       <c r="R5" t="n">
-        <v>6520773</v>
+        <v>6520712</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1128,13 +1141,17 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>En hane i sitt revir som hördes flera gånger som sedan landat på stambasen av en tall och började söka föda innan den skrämdes av mig.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1153,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120453858</v>
+        <v>120453442</v>
       </c>
       <c r="B6" t="n">
-        <v>92048</v>
+        <v>94704</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,30 +1182,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1196,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>313282</v>
+        <v>313613</v>
       </c>
       <c r="R6" t="n">
-        <v>6521011</v>
+        <v>6520747</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1226,17 +1244,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ett fint exemplar som i bilderboken på rätt substrat och i rätt miljö dvs. senvuxen och riktig gammal tallnaturskog med urskogsartad karaktär.</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120453364</v>
+        <v>120453471</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>91192</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,28 +1293,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>5454</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1311,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>313632</v>
+        <v>313508</v>
       </c>
       <c r="R7" t="n">
-        <v>6520770</v>
+        <v>6520766</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1374,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120453528</v>
+        <v>120453424</v>
       </c>
       <c r="B8" t="n">
-        <v>79160</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,26 +1399,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1417,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>313517</v>
+        <v>313613</v>
       </c>
       <c r="R8" t="n">
-        <v>6520845</v>
+        <v>6520747</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1461,7 +1475,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1480,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120453741</v>
+        <v>120454016</v>
       </c>
       <c r="B9" t="n">
-        <v>79160</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,26 +1509,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1523,10 +1537,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>313401</v>
+        <v>313279</v>
       </c>
       <c r="R9" t="n">
-        <v>6521033</v>
+        <v>6520849</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1561,13 +1575,17 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1586,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120453745</v>
+        <v>120453719</v>
       </c>
       <c r="B10" t="n">
-        <v>57202</v>
+        <v>79160</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,27 +1620,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100011</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1630,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>313401</v>
+        <v>313475</v>
       </c>
       <c r="R10" t="n">
-        <v>6521033</v>
+        <v>6520948</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1674,6 +1691,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1692,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120453982</v>
+        <v>120453763</v>
       </c>
       <c r="B11" t="n">
-        <v>56532</v>
+        <v>79160</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,43 +1722,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1748,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>313285</v>
+        <v>313385</v>
       </c>
       <c r="R11" t="n">
-        <v>6520925</v>
+        <v>6521062</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1786,17 +1791,13 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>En hona och det sågs även tidigare en hona samt även en tupp i området.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1815,10 +1816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120454041</v>
+        <v>120453447</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
+        <v>94433</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,35 +1828,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1863,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>313277</v>
+        <v>313613</v>
       </c>
       <c r="R12" t="n">
-        <v>6520849</v>
+        <v>6520747</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1893,12 +1890,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,6 +1904,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1925,10 +1923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120454259</v>
+        <v>120453474</v>
       </c>
       <c r="B13" t="n">
-        <v>91192</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,26 +1939,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5454</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1968,10 +1971,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>313665</v>
+        <v>313546</v>
       </c>
       <c r="R13" t="n">
-        <v>6520570</v>
+        <v>6520792</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1998,12 +2001,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,7 +2015,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2031,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120453956</v>
+        <v>120453798</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>79160</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,31 +2049,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2079,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>313269</v>
+        <v>313302</v>
       </c>
       <c r="R14" t="n">
-        <v>6520997</v>
+        <v>6521038</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2117,17 +2114,13 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Troligen en hane men lite svår att exakt se när han flög förbi.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2146,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120453731</v>
+        <v>120453488</v>
       </c>
       <c r="B15" t="n">
-        <v>79160</v>
+        <v>57336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,26 +2155,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2189,10 +2187,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>313412</v>
+        <v>313547</v>
       </c>
       <c r="R15" t="n">
-        <v>6521002</v>
+        <v>6520844</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2219,12 +2217,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2233,7 +2231,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2252,10 +2249,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120453391</v>
+        <v>120453956</v>
       </c>
       <c r="B16" t="n">
-        <v>94704</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,31 +2261,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2296,10 +2297,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>313617</v>
+        <v>313269</v>
       </c>
       <c r="R16" t="n">
-        <v>6520749</v>
+        <v>6520997</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2326,12 +2327,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Troligen en hane men lite svår att exakt se när han flög förbi.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2340,7 +2346,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2359,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120453310</v>
+        <v>120453741</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>79160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2375,31 +2380,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>313673</v>
+        <v>313401</v>
       </c>
       <c r="R17" t="n">
-        <v>6520528</v>
+        <v>6521033</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,6 +2451,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2469,10 +2470,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120453424</v>
+        <v>120454251</v>
       </c>
       <c r="B18" t="n">
-        <v>57336</v>
+        <v>56532</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2481,35 +2482,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2517,10 +2526,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>313613</v>
+        <v>313460</v>
       </c>
       <c r="R18" t="n">
-        <v>6520747</v>
+        <v>6520664</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2547,12 +2556,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>En gammal tupp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,10 +2593,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120454114</v>
+        <v>120453391</v>
       </c>
       <c r="B19" t="n">
-        <v>94433</v>
+        <v>94704</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,21 +2609,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2667</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2637,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>313253</v>
+        <v>313617</v>
       </c>
       <c r="R19" t="n">
-        <v>6520846</v>
+        <v>6520749</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2653,12 +2667,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2792,7 +2806,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120453330</v>
+        <v>120453460</v>
       </c>
       <c r="B21" t="n">
         <v>79160</v>
@@ -2835,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>313727</v>
+        <v>313498</v>
       </c>
       <c r="R21" t="n">
-        <v>6520657</v>
+        <v>6520773</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2898,10 +2912,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120453698</v>
+        <v>120453330</v>
       </c>
       <c r="B22" t="n">
-        <v>57473</v>
+        <v>79160</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2914,35 +2928,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2950,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>313500</v>
+        <v>313727</v>
       </c>
       <c r="R22" t="n">
-        <v>6520930</v>
+        <v>6520657</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2980,17 +2985,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ett stationär par med två än så länge kvarvarande ungar</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2999,6 +2999,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3017,10 +3018,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120453798</v>
+        <v>120453698</v>
       </c>
       <c r="B23" t="n">
-        <v>79160</v>
+        <v>57473</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3033,26 +3034,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3060,10 +3070,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>313302</v>
+        <v>313500</v>
       </c>
       <c r="R23" t="n">
-        <v>6521038</v>
+        <v>6520930</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3098,13 +3108,17 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ett stationär par med två än så länge kvarvarande ungar</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3123,10 +3137,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120453488</v>
+        <v>120453528</v>
       </c>
       <c r="B24" t="n">
-        <v>57336</v>
+        <v>79160</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3139,31 +3153,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3171,10 +3180,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>313547</v>
+        <v>313517</v>
       </c>
       <c r="R24" t="n">
-        <v>6520844</v>
+        <v>6520845</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3215,6 +3224,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3233,10 +3243,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120453313</v>
+        <v>120453982</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>56532</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3245,33 +3255,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3281,10 +3299,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>313719</v>
+        <v>313285</v>
       </c>
       <c r="R25" t="n">
-        <v>6520649</v>
+        <v>6520925</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3311,12 +3329,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>En hona och det sågs även tidigare en hona samt även en tupp i området.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3343,10 +3366,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120453474</v>
+        <v>120454114</v>
       </c>
       <c r="B26" t="n">
-        <v>57336</v>
+        <v>94433</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3355,35 +3378,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>2667</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3391,10 +3410,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>313546</v>
+        <v>313253</v>
       </c>
       <c r="R26" t="n">
-        <v>6520792</v>
+        <v>6520846</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3421,12 +3440,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3435,6 +3454,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3453,10 +3473,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120453442</v>
+        <v>120453313</v>
       </c>
       <c r="B27" t="n">
-        <v>94704</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3465,31 +3485,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3497,10 +3521,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>313613</v>
+        <v>313719</v>
       </c>
       <c r="R27" t="n">
-        <v>6520747</v>
+        <v>6520649</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3541,7 +3565,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3560,10 +3583,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120453531</v>
+        <v>120452908</v>
       </c>
       <c r="B28" t="n">
-        <v>90804</v>
+        <v>90848</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3572,25 +3595,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1102</v>
+        <v>71</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gäckporing</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Postia parva</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Renvall) Renvall</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3603,10 +3626,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>313519</v>
+        <v>313704</v>
       </c>
       <c r="R28" t="n">
-        <v>6520864</v>
+        <v>6520606</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3639,6 +3662,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Jag vet, att fyndet är mycket anmärkningsvärt i den delen av landet och jag själv kunde knappast tro det,för fyndet ligger utanför där jag själv och andra har rapporterad fynd för arten. Den brukar vanligen förekomma sparsam i norra Norrlands inland ner till norra Värmland. Men nu är det faktiskt så att Bohuslän/Dalsland har åtminstone i de norra delarna aldrig varit skogslösa som det påstås. I det trakter där fyndet gjorts finns faktiskt urskogsartad skog enligt definition  med en skoglig kontinuitet som sträcker sig åtminstone till 1680. Historisk källmaterial berättar om att även under den mest skogslösa tiden dvs. i mitten av 1800 talet om djup skogsbygd med timmerskogar i trakten. Faktum är att jag för två år sedan hade ytterligare ett fynd av urskogsporing i ett närbelägäget område som kyrkan ville hugga, då vågade jag inte att rapportera in för jag aldrig tidigare under nästan 30 år med skoglig naturvärdesinventering åt alla aktörer i landet varit med om liknande.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3666,10 +3694,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120453763</v>
+        <v>120454108</v>
       </c>
       <c r="B29" t="n">
-        <v>79160</v>
+        <v>57336</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3682,26 +3710,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3709,10 +3742,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>313385</v>
+        <v>313253</v>
       </c>
       <c r="R29" t="n">
-        <v>6521062</v>
+        <v>6520846</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3747,13 +3780,17 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Tydliga hackspår</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3772,10 +3809,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120453987</v>
+        <v>120453745</v>
       </c>
       <c r="B30" t="n">
-        <v>79160</v>
+        <v>57202</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3788,26 +3825,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>100011</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3815,10 +3853,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>313285</v>
+        <v>313401</v>
       </c>
       <c r="R30" t="n">
-        <v>6520925</v>
+        <v>6521033</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3859,7 +3897,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3878,10 +3915,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120454233</v>
+        <v>120453531</v>
       </c>
       <c r="B31" t="n">
-        <v>90600</v>
+        <v>90804</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3894,21 +3931,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>1102</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gäckporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Postia parva</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Renvall) Renvall</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3921,10 +3958,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>313395</v>
+        <v>313519</v>
       </c>
       <c r="R31" t="n">
-        <v>6520717</v>
+        <v>6520864</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3951,17 +3988,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ett litet och undangömd exemplar på en av gammeltallarna</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3989,7 +4021,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120453342</v>
+        <v>120453817</v>
       </c>
       <c r="B32" t="n">
         <v>57336</v>
@@ -4022,20 +4054,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4045,10 +4069,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>313691</v>
+        <v>313287</v>
       </c>
       <c r="R32" t="n">
-        <v>6520712</v>
+        <v>6521023</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4075,17 +4099,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>En hane i sitt revir som hördes flera gånger som sedan landat på stambasen av en tall och började söka föda innan den skrämdes av mig.</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4112,10 +4131,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120453447</v>
+        <v>120453858</v>
       </c>
       <c r="B33" t="n">
-        <v>94433</v>
+        <v>92048</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4124,31 +4143,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2667</v>
+        <v>2079</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4156,10 +4174,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>313613</v>
+        <v>313282</v>
       </c>
       <c r="R33" t="n">
-        <v>6520747</v>
+        <v>6521011</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4186,12 +4204,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ett fint exemplar som i bilderboken på rätt substrat och i rätt miljö dvs. senvuxen och riktig gammal tallnaturskog med urskogsartad karaktär.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4219,10 +4242,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120453817</v>
+        <v>120454259</v>
       </c>
       <c r="B34" t="n">
-        <v>57336</v>
+        <v>91192</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4235,31 +4258,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>5454</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4267,10 +4285,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>313287</v>
+        <v>313665</v>
       </c>
       <c r="R34" t="n">
-        <v>6521023</v>
+        <v>6520570</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4311,6 +4329,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4329,10 +4348,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120454016</v>
+        <v>120454233</v>
       </c>
       <c r="B35" t="n">
-        <v>57336</v>
+        <v>90600</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4345,27 +4364,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4373,10 +4391,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>313279</v>
+        <v>313395</v>
       </c>
       <c r="R35" t="n">
-        <v>6520849</v>
+        <v>6520717</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4413,7 +4431,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Ett litet och undangömd exemplar på en av gammeltallarna</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4422,6 +4440,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4440,10 +4459,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120453471</v>
+        <v>120453731</v>
       </c>
       <c r="B36" t="n">
-        <v>91192</v>
+        <v>79160</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4456,21 +4475,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5454</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4483,10 +4502,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>313508</v>
+        <v>313412</v>
       </c>
       <c r="R36" t="n">
-        <v>6520766</v>
+        <v>6521002</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4513,12 +4532,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4546,10 +4565,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120452908</v>
+        <v>120453364</v>
       </c>
       <c r="B37" t="n">
-        <v>90848</v>
+        <v>91881</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4558,28 +4577,32 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>71</v>
+        <v>5966</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4589,10 +4612,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>313704</v>
+        <v>313632</v>
       </c>
       <c r="R37" t="n">
-        <v>6520606</v>
+        <v>6520770</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4625,11 +4648,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-14</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Jag vet, att fyndet är mycket anmärkningsvärt i den delen av landet och jag själv kunde knappast tro det,för fyndet ligger utanför där jag själv och andra har rapporterad fynd för arten. Den brukar vanligen förekomma sparsam i norra Norrlands inland ner till norra Värmland. Men nu är det faktiskt så att Bohuslän/Dalsland har åtminstone i de norra delarna aldrig varit skogslösa som det påstås. I det trakter där fyndet gjorts finns faktiskt urskogsartad skog enligt definition  med en skoglig kontinuitet som sträcker sig åtminstone till 1680. Historisk källmaterial berättar om att även under den mest skogslösa tiden dvs. i mitten av 1800 talet om djup skogsbygd med timmerskogar i trakten. Faktum är att jag för två år sedan hade ytterligare ett fynd av urskogsporing i ett närbelägäget område som kyrkan ville hugga, då vågade jag inte att rapportera in för jag aldrig tidigare under nästan 30 år med skoglig naturvärdesinventering åt alla aktörer i landet varit med om liknande.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4657,10 +4675,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120454108</v>
+        <v>120453481</v>
       </c>
       <c r="B38" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4673,16 +4691,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4705,10 +4723,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>313253</v>
+        <v>313558</v>
       </c>
       <c r="R38" t="n">
-        <v>6520846</v>
+        <v>6520816</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4735,17 +4753,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Tydliga hackspår</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4891,10 +4904,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120453996</v>
+        <v>120453987</v>
       </c>
       <c r="B40" t="n">
-        <v>91870</v>
+        <v>79160</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4903,25 +4916,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4934,10 +4947,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>313291</v>
+        <v>313285</v>
       </c>
       <c r="R40" t="n">
-        <v>6520882</v>
+        <v>6520925</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4997,10 +5010,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120453481</v>
+        <v>120454041</v>
       </c>
       <c r="B41" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5013,16 +5026,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5045,10 +5058,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>313558</v>
+        <v>313277</v>
       </c>
       <c r="R41" t="n">
-        <v>6520816</v>
+        <v>6520849</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5075,12 +5088,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5107,10 +5120,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120453719</v>
+        <v>120453996</v>
       </c>
       <c r="B42" t="n">
-        <v>79160</v>
+        <v>91870</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5119,25 +5132,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5150,10 +5163,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>313475</v>
+        <v>313291</v>
       </c>
       <c r="R42" t="n">
-        <v>6520948</v>
+        <v>6520882</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5213,10 +5226,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120454251</v>
+        <v>120453310</v>
       </c>
       <c r="B43" t="n">
-        <v>56532</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5225,43 +5238,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5269,10 +5274,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>313460</v>
+        <v>313673</v>
       </c>
       <c r="R43" t="n">
-        <v>6520664</v>
+        <v>6520528</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5299,17 +5304,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>En gammal tupp</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 33012-2024 artfynd.xlsx
+++ b/artfynd/A 33012-2024 artfynd.xlsx
@@ -1493,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120454016</v>
+        <v>120453447</v>
       </c>
       <c r="B9" t="n">
-        <v>57336</v>
+        <v>94433</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,31 +1505,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2667</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>313279</v>
+        <v>313613</v>
       </c>
       <c r="R9" t="n">
-        <v>6520849</v>
+        <v>6520747</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1567,17 +1567,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,6 +1581,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1604,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120453719</v>
+        <v>120454016</v>
       </c>
       <c r="B10" t="n">
-        <v>79160</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,26 +1616,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1647,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>313475</v>
+        <v>313279</v>
       </c>
       <c r="R10" t="n">
-        <v>6520948</v>
+        <v>6520849</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1685,13 +1682,17 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1710,7 +1711,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120453763</v>
+        <v>120453719</v>
       </c>
       <c r="B11" t="n">
         <v>79160</v>
@@ -1753,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>313385</v>
+        <v>313475</v>
       </c>
       <c r="R11" t="n">
-        <v>6521062</v>
+        <v>6520948</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1816,10 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120453447</v>
+        <v>120453763</v>
       </c>
       <c r="B12" t="n">
-        <v>94433</v>
+        <v>79160</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,31 +1829,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2667</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>313613</v>
+        <v>313385</v>
       </c>
       <c r="R12" t="n">
-        <v>6520747</v>
+        <v>6521062</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1890,12 +1890,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -3137,10 +3137,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120453528</v>
+        <v>120454114</v>
       </c>
       <c r="B24" t="n">
-        <v>79160</v>
+        <v>94433</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3149,30 +3149,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>2667</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3180,10 +3181,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>313517</v>
+        <v>313253</v>
       </c>
       <c r="R24" t="n">
-        <v>6520845</v>
+        <v>6520846</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3210,12 +3211,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3243,10 +3244,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120453982</v>
+        <v>120453528</v>
       </c>
       <c r="B25" t="n">
-        <v>56532</v>
+        <v>79160</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3255,43 +3256,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3299,10 +3287,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>313285</v>
+        <v>313517</v>
       </c>
       <c r="R25" t="n">
-        <v>6520925</v>
+        <v>6520845</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3329,17 +3317,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>En hona och det sågs även tidigare en hona samt även en tupp i området.</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,6 +3331,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3366,10 +3350,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120454114</v>
+        <v>120453982</v>
       </c>
       <c r="B26" t="n">
-        <v>94433</v>
+        <v>56532</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3382,27 +3366,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2667</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3410,10 +3406,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>313253</v>
+        <v>313285</v>
       </c>
       <c r="R26" t="n">
-        <v>6520846</v>
+        <v>6520925</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3448,13 +3444,17 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>En hona och det sågs även tidigare en hona samt även en tupp i området.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3583,10 +3583,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120452908</v>
+        <v>120454108</v>
       </c>
       <c r="B28" t="n">
-        <v>90848</v>
+        <v>57336</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3595,30 +3595,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>71</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3626,10 +3631,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>313704</v>
+        <v>313253</v>
       </c>
       <c r="R28" t="n">
-        <v>6520606</v>
+        <v>6520846</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3656,17 +3661,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Jag vet, att fyndet är mycket anmärkningsvärt i den delen av landet och jag själv kunde knappast tro det,för fyndet ligger utanför där jag själv och andra har rapporterad fynd för arten. Den brukar vanligen förekomma sparsam i norra Norrlands inland ner till norra Värmland. Men nu är det faktiskt så att Bohuslän/Dalsland har åtminstone i de norra delarna aldrig varit skogslösa som det påstås. I det trakter där fyndet gjorts finns faktiskt urskogsartad skog enligt definition  med en skoglig kontinuitet som sträcker sig åtminstone till 1680. Historisk källmaterial berättar om att även under den mest skogslösa tiden dvs. i mitten av 1800 talet om djup skogsbygd med timmerskogar i trakten. Faktum är att jag för två år sedan hade ytterligare ett fynd av urskogsporing i ett närbelägäget område som kyrkan ville hugga, då vågade jag inte att rapportera in för jag aldrig tidigare under nästan 30 år med skoglig naturvärdesinventering åt alla aktörer i landet varit med om liknande.</t>
+          <t>Tydliga hackspår</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3675,7 +3680,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3694,10 +3698,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120454108</v>
+        <v>120453745</v>
       </c>
       <c r="B29" t="n">
-        <v>57336</v>
+        <v>57202</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3710,16 +3714,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100011</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3730,11 +3734,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>313253</v>
+        <v>313401</v>
       </c>
       <c r="R29" t="n">
-        <v>6520846</v>
+        <v>6521033</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3778,11 +3778,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Tydliga hackspår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3809,10 +3804,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120453745</v>
+        <v>120452908</v>
       </c>
       <c r="B30" t="n">
-        <v>57202</v>
+        <v>90848</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3821,31 +3816,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100011</v>
+        <v>71</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3853,10 +3847,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>313401</v>
+        <v>313704</v>
       </c>
       <c r="R30" t="n">
-        <v>6521033</v>
+        <v>6520606</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3883,12 +3877,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Jag vet, att fyndet är mycket anmärkningsvärt i den delen av landet och jag själv kunde knappast tro det,för fyndet ligger utanför där jag själv och andra har rapporterad fynd för arten. Den brukar vanligen förekomma sparsam i norra Norrlands inland ner till norra Värmland. Men nu är det faktiskt så att Bohuslän/Dalsland har åtminstone i de norra delarna aldrig varit skogslösa som det påstås. I det trakter där fyndet gjorts finns faktiskt urskogsartad skog enligt definition  med en skoglig kontinuitet som sträcker sig åtminstone till 1680. Historisk källmaterial berättar om att även under den mest skogslösa tiden dvs. i mitten av 1800 talet om djup skogsbygd med timmerskogar i trakten. Faktum är att jag för två år sedan hade ytterligare ett fynd av urskogsporing i ett närbelägäget område som kyrkan ville hugga, då vågade jag inte att rapportera in för jag aldrig tidigare under nästan 30 år med skoglig naturvärdesinventering åt alla aktörer i landet varit med om liknande.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3897,6 +3896,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3915,10 +3915,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120453531</v>
+        <v>120453817</v>
       </c>
       <c r="B31" t="n">
-        <v>90804</v>
+        <v>57336</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3931,26 +3931,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1102</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gäckporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Postia parva</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Renvall) Renvall</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3958,10 +3963,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>313519</v>
+        <v>313287</v>
       </c>
       <c r="R31" t="n">
-        <v>6520864</v>
+        <v>6521023</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3988,12 +3993,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4002,7 +4007,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4021,10 +4025,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120453817</v>
+        <v>120453531</v>
       </c>
       <c r="B32" t="n">
-        <v>57336</v>
+        <v>90804</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4037,31 +4041,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>1102</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gäckporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Postia parva</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Renvall) Renvall</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4069,10 +4068,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>313287</v>
+        <v>313519</v>
       </c>
       <c r="R32" t="n">
-        <v>6521023</v>
+        <v>6520864</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4099,12 +4098,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4113,6 +4112,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33012-2024 artfynd.xlsx
+++ b/artfynd/A 33012-2024 artfynd.xlsx
@@ -5228,7 +5228,7 @@
         <v>120452908</v>
       </c>
       <c r="B43" t="n">
-        <v>90957</v>
+        <v>90967</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>

--- a/artfynd/A 33012-2024 artfynd.xlsx
+++ b/artfynd/A 33012-2024 artfynd.xlsx
@@ -5228,7 +5228,7 @@
         <v>120452908</v>
       </c>
       <c r="B43" t="n">
-        <v>90967</v>
+        <v>90979</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>

--- a/artfynd/A 33012-2024 artfynd.xlsx
+++ b/artfynd/A 33012-2024 artfynd.xlsx
@@ -4722,7 +4722,7 @@
         <v>120391273</v>
       </c>
       <c r="B39" t="n">
-        <v>56560</v>
+        <v>56688</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>120453982</v>
       </c>
       <c r="B40" t="n">
-        <v>56560</v>
+        <v>56688</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>120454251</v>
       </c>
       <c r="B41" t="n">
-        <v>56560</v>
+        <v>56688</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 33012-2024 artfynd.xlsx
+++ b/artfynd/A 33012-2024 artfynd.xlsx
@@ -4722,7 +4722,7 @@
         <v>120391273</v>
       </c>
       <c r="B39" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>120453982</v>
       </c>
       <c r="B40" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>120454251</v>
       </c>
       <c r="B41" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 33012-2024 artfynd.xlsx
+++ b/artfynd/A 33012-2024 artfynd.xlsx
@@ -4722,7 +4722,7 @@
         <v>120391273</v>
       </c>
       <c r="B39" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>120453982</v>
       </c>
       <c r="B40" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>120454251</v>
       </c>
       <c r="B41" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 33012-2024 artfynd.xlsx
+++ b/artfynd/A 33012-2024 artfynd.xlsx
@@ -4722,7 +4722,7 @@
         <v>120391273</v>
       </c>
       <c r="B39" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>120453982</v>
       </c>
       <c r="B40" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>120454251</v>
       </c>
       <c r="B41" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 33012-2024 artfynd.xlsx
+++ b/artfynd/A 33012-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,44 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120389662</v>
+        <v>120452908</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4363</v>
+        <v>71</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -722,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>313719</v>
+        <v>313704</v>
       </c>
       <c r="R2" t="n">
-        <v>6520439</v>
+        <v>6520606</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -752,12 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Jag vet, att fyndet är mycket anmärkningsvärt i den delen av landet och jag själv kunde knappast tro det,för fyndet ligger utanför där jag själv och andra har rapporterad fynd för arten. Den brukar vanligen förekomma sparsam i norra Norrlands inland ner till norra Värmland. Men nu är det faktiskt så att Bohuslän/Dalsland har åtminstone i de norra delarna aldrig varit skogslösa som det påstås. I det trakter där fyndet gjorts finns faktiskt urskogsartad skog enligt definition  med en skoglig kontinuitet som sträcker sig åtminstone till 1680. Historisk källmaterial berättar om att även under den mest skogslösa tiden dvs. i mitten av 1800 talet om djup skogsbygd med timmerskogar i trakten. Faktum är att jag för två år sedan hade ytterligare ett fynd av urskogsporing i ett närbelägäget område som kyrkan ville hugga, då vågade jag inte att rapportera in för jag aldrig tidigare under nästan 30 år med skoglig naturvärdesinventering åt alla aktörer i landet varit med om liknande.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120391210</v>
+        <v>120453531</v>
       </c>
       <c r="B3" t="n">
-        <v>57351</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92157</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,45 +792,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1102</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gäckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Postia parva</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Renvall) Renvall</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>munkedal Krokstad, Boh</t>
+          <t>Hälletjärnet , Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>313613</v>
+        <v>313519</v>
       </c>
       <c r="R3" t="n">
-        <v>6520749</v>
+        <v>6520864</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,27 +849,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hack basen död tall</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,33 +863,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120453460</v>
+        <v>120389655</v>
       </c>
       <c r="B4" t="n">
-        <v>79208</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>313498</v>
+        <v>313669</v>
       </c>
       <c r="R4" t="n">
-        <v>6520773</v>
+        <v>6520443</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,12 +950,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,15 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120454041</v>
+        <v>120453858</v>
       </c>
       <c r="B5" t="n">
-        <v>57360</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,31 +994,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1064,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>313277</v>
+        <v>313282</v>
       </c>
       <c r="R5" t="n">
-        <v>6520849</v>
+        <v>6521011</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,12 +1059,18 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ett fint exemplar som i bilderboken på rätt substrat och i rätt miljö dvs. senvuxen och riktig gammal tallnaturskog med urskogsartad karaktär.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1126,51 +1089,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120453438</v>
+        <v>120453391</v>
       </c>
       <c r="B6" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1178,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>313613</v>
+        <v>313617</v>
       </c>
       <c r="R6" t="n">
-        <v>6520747</v>
+        <v>6520749</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,17 +1166,13 @@
           <t>2024-10-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ett par I sitt revir med tydligen 2 av årets ungar som än så länge toleras i reviret.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1245,15 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120453391</v>
+        <v>120453442</v>
       </c>
       <c r="B7" t="n">
-        <v>94813</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>313617</v>
+        <v>313613</v>
       </c>
       <c r="R7" t="n">
-        <v>6520749</v>
+        <v>6520747</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1352,51 +1293,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120453698</v>
+        <v>120453447</v>
       </c>
       <c r="B8" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>2667</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1404,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>313500</v>
+        <v>313613</v>
       </c>
       <c r="R8" t="n">
-        <v>6520930</v>
+        <v>6520747</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1434,17 +1362,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ett stationär par med två än så länge kvarvarande ungar</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,6 +1376,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1471,42 +1395,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120453330</v>
+        <v>120454114</v>
       </c>
       <c r="B9" t="n">
-        <v>79208</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>2667</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1514,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>313727</v>
+        <v>313253</v>
       </c>
       <c r="R9" t="n">
-        <v>6520657</v>
+        <v>6520846</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1544,12 +1464,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,15 +1497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120453442</v>
+        <v>120389662</v>
       </c>
       <c r="B10" t="n">
-        <v>94813</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,27 +1508,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>4363</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1621,10 +1539,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>313613</v>
+        <v>313719</v>
       </c>
       <c r="R10" t="n">
-        <v>6520747</v>
+        <v>6520439</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1651,12 +1569,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,15 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120453323</v>
+        <v>120453996</v>
       </c>
       <c r="B11" t="n">
-        <v>91282</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,21 +1613,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5454</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>313723</v>
+        <v>313291</v>
       </c>
       <c r="R11" t="n">
-        <v>6520673</v>
+        <v>6520882</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1757,12 +1670,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,37 +1703,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120453858</v>
+        <v>120453672</v>
       </c>
       <c r="B12" t="n">
-        <v>92142</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>4787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1833,10 +1741,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>313282</v>
+        <v>313523</v>
       </c>
       <c r="R12" t="n">
-        <v>6521011</v>
+        <v>6520967</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1869,11 +1777,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ett fint exemplar som i bilderboken på rätt substrat och i rätt miljö dvs. senvuxen och riktig gammal tallnaturskog med urskogsartad karaktär.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,15 +1804,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120454016</v>
+        <v>120454233</v>
       </c>
       <c r="B13" t="n">
-        <v>57360</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,27 +1815,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1945,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>313279</v>
+        <v>313395</v>
       </c>
       <c r="R13" t="n">
-        <v>6520849</v>
+        <v>6520717</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1985,7 +1882,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Ett litet och undangömd exemplar på en av gammeltallarna</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,6 +1891,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2012,15 +1910,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120453531</v>
+        <v>120453323</v>
       </c>
       <c r="B14" t="n">
-        <v>90898</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92556</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2028,21 +1921,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1102</v>
+        <v>5454</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gäckporing</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Postia parva</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Renvall) Renvall</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2055,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>313519</v>
+        <v>313723</v>
       </c>
       <c r="R14" t="n">
-        <v>6520864</v>
+        <v>6520673</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2118,15 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120453364</v>
+        <v>120453471</v>
       </c>
       <c r="B15" t="n">
-        <v>91980</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92556</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2134,28 +2022,24 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>5454</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2165,10 +2049,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>313632</v>
+        <v>313508</v>
       </c>
       <c r="R15" t="n">
-        <v>6520770</v>
+        <v>6520766</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2228,15 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120453763</v>
+        <v>120454259</v>
       </c>
       <c r="B16" t="n">
-        <v>79208</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92556</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,21 +2123,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5454</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,10 +2150,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>313385</v>
+        <v>313665</v>
       </c>
       <c r="R16" t="n">
-        <v>6521062</v>
+        <v>6520570</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2334,15 +2213,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120453956</v>
+        <v>120453364</v>
       </c>
       <c r="B17" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2350,31 +2224,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2382,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>313269</v>
+        <v>313632</v>
       </c>
       <c r="R17" t="n">
-        <v>6520997</v>
+        <v>6520770</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2412,17 +2285,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Troligen en hane men lite svår att exakt se när han flög förbi.</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,6 +2299,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2449,15 +2318,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120453313</v>
+        <v>120453330</v>
       </c>
       <c r="B18" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,31 +2329,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2497,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>313719</v>
+        <v>313727</v>
       </c>
       <c r="R18" t="n">
-        <v>6520649</v>
+        <v>6520657</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2541,6 +2400,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2559,15 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120453817</v>
+        <v>120453460</v>
       </c>
       <c r="B19" t="n">
-        <v>57360</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2575,31 +2430,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2607,10 +2457,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>313287</v>
+        <v>313498</v>
       </c>
       <c r="R19" t="n">
-        <v>6521023</v>
+        <v>6520773</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2637,12 +2487,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2651,6 +2501,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2669,15 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120453424</v>
+        <v>120453528</v>
       </c>
       <c r="B20" t="n">
-        <v>57360</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,31 +2531,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2717,10 +2558,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>313613</v>
+        <v>313517</v>
       </c>
       <c r="R20" t="n">
-        <v>6520747</v>
+        <v>6520845</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2761,6 +2602,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2779,15 +2621,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120453310</v>
+        <v>120453719</v>
       </c>
       <c r="B21" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2795,31 +2632,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2827,10 +2659,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>313673</v>
+        <v>313475</v>
       </c>
       <c r="R21" t="n">
-        <v>6520528</v>
+        <v>6520948</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2857,12 +2689,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2871,6 +2703,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2889,15 +2722,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120453987</v>
+        <v>120453731</v>
       </c>
       <c r="B22" t="n">
-        <v>79208</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2932,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>313285</v>
+        <v>313412</v>
       </c>
       <c r="R22" t="n">
-        <v>6520925</v>
+        <v>6521002</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2998,12 +2826,7 @@
         <v>120453741</v>
       </c>
       <c r="B23" t="n">
-        <v>79208</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3101,15 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120453481</v>
+        <v>120453763</v>
       </c>
       <c r="B24" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,31 +2935,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3149,10 +2962,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>313558</v>
+        <v>313385</v>
       </c>
       <c r="R24" t="n">
-        <v>6520816</v>
+        <v>6521062</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3179,12 +2992,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3193,6 +3006,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3211,15 +3025,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120453731</v>
+        <v>120453798</v>
       </c>
       <c r="B25" t="n">
-        <v>79208</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3254,10 +3063,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>313412</v>
+        <v>313302</v>
       </c>
       <c r="R25" t="n">
-        <v>6521002</v>
+        <v>6521038</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3317,15 +3126,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120453488</v>
+        <v>120453987</v>
       </c>
       <c r="B26" t="n">
-        <v>57360</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3333,31 +3137,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3365,10 +3164,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>313547</v>
+        <v>313285</v>
       </c>
       <c r="R26" t="n">
-        <v>6520844</v>
+        <v>6520925</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3395,12 +3194,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3409,6 +3208,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3427,43 +3227,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120454114</v>
+        <v>120453745</v>
       </c>
       <c r="B27" t="n">
-        <v>94542</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2667</v>
+        <v>100011</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3471,10 +3266,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>313253</v>
+        <v>313401</v>
       </c>
       <c r="R27" t="n">
-        <v>6520846</v>
+        <v>6521033</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3515,7 +3310,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3534,42 +3328,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120454259</v>
+        <v>120389649</v>
       </c>
       <c r="B28" t="n">
-        <v>91282</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5454</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3577,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>313665</v>
+        <v>313669</v>
       </c>
       <c r="R28" t="n">
-        <v>6520570</v>
+        <v>6520443</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3607,12 +3397,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3621,7 +3411,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3640,56 +3429,52 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120453471</v>
+        <v>120391017</v>
       </c>
       <c r="B29" t="n">
-        <v>91282</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5454</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hälletjärnet , Boh</t>
+          <t>Munkedal Kroksatad, Boh</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>313508</v>
+        <v>313672</v>
       </c>
       <c r="R29" t="n">
-        <v>6520766</v>
+        <v>6520445</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3713,12 +3498,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hack i död gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3727,38 +3527,32 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120453474</v>
+        <v>120391210</v>
       </c>
       <c r="B30" t="n">
-        <v>57360</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3779,28 +3573,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hälletjärnet , Boh</t>
+          <t>munkedal Krokstad, Boh</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>313546</v>
+        <v>313613</v>
       </c>
       <c r="R30" t="n">
-        <v>6520792</v>
+        <v>6520749</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3824,12 +3618,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hack basen död tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3844,54 +3653,62 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120454233</v>
+        <v>120453342</v>
       </c>
       <c r="B31" t="n">
-        <v>90690</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3899,10 +3716,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>313395</v>
+        <v>313691</v>
       </c>
       <c r="R31" t="n">
-        <v>6520717</v>
+        <v>6520712</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3929,17 +3746,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ett litet och undangömd exemplar på en av gammeltallarna</t>
+          <t>En hane i sitt revir som hördes flera gånger som sedan landat på stambasen av en tall och började söka föda innan den skrämdes av mig.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3948,7 +3765,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3967,19 +3783,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120454108</v>
+        <v>120453424</v>
       </c>
       <c r="B32" t="n">
-        <v>57360</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4015,10 +3826,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>313253</v>
+        <v>313613</v>
       </c>
       <c r="R32" t="n">
-        <v>6520846</v>
+        <v>6520747</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4045,17 +3856,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Tydliga hackspår</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4082,42 +3888,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120453798</v>
+        <v>120453474</v>
       </c>
       <c r="B33" t="n">
-        <v>79208</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4125,10 +3931,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>313302</v>
+        <v>313546</v>
       </c>
       <c r="R33" t="n">
-        <v>6521038</v>
+        <v>6520792</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4155,12 +3961,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4169,7 +3975,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4188,42 +3993,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120453528</v>
+        <v>120453488</v>
       </c>
       <c r="B34" t="n">
-        <v>79208</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4231,10 +4036,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>313517</v>
+        <v>313547</v>
       </c>
       <c r="R34" t="n">
-        <v>6520845</v>
+        <v>6520844</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4275,7 +4080,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4294,42 +4098,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120453719</v>
+        <v>120453817</v>
       </c>
       <c r="B35" t="n">
-        <v>79208</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4337,10 +4141,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>313475</v>
+        <v>313287</v>
       </c>
       <c r="R35" t="n">
-        <v>6520948</v>
+        <v>6521023</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4381,7 +4185,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4400,15 +4203,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120453447</v>
+        <v>120454016</v>
       </c>
       <c r="B36" t="n">
-        <v>94542</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4416,27 +4214,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2667</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4444,10 +4242,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>313613</v>
+        <v>313279</v>
       </c>
       <c r="R36" t="n">
-        <v>6520747</v>
+        <v>6520849</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4474,12 +4272,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4488,7 +4291,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4507,15 +4309,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120453996</v>
+        <v>120454041</v>
       </c>
       <c r="B37" t="n">
-        <v>91957</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4523,26 +4320,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4550,10 +4352,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>313291</v>
+        <v>313277</v>
       </c>
       <c r="R37" t="n">
-        <v>6520882</v>
+        <v>6520849</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4594,7 +4396,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4613,32 +4414,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120453745</v>
+        <v>120454108</v>
       </c>
       <c r="B38" t="n">
-        <v>57230</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100011</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4649,7 +4445,11 @@
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4657,10 +4457,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>313401</v>
+        <v>313253</v>
       </c>
       <c r="R38" t="n">
-        <v>6521033</v>
+        <v>6520846</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4693,6 +4493,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Tydliga hackspår</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4719,15 +4524,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120391273</v>
+        <v>120454136</v>
       </c>
       <c r="B39" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4735,57 +4535,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Munkedal Krokstad, Boh</t>
+          <t>Hälletjärnet , Boh</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>313609</v>
+        <v>313259</v>
       </c>
       <c r="R39" t="n">
-        <v>6520729</v>
+        <v>6520816</v>
       </c>
       <c r="S39" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4809,22 +4597,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4835,74 +4613,56 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120453982</v>
+        <v>120453310</v>
       </c>
       <c r="B40" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4912,10 +4672,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>313285</v>
+        <v>313673</v>
       </c>
       <c r="R40" t="n">
-        <v>6520925</v>
+        <v>6520528</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4942,17 +4702,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>En hona och det sågs även tidigare en hona samt även en tupp i området.</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4979,55 +4734,42 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120454251</v>
+        <v>120453313</v>
       </c>
       <c r="B41" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5035,10 +4777,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>313460</v>
+        <v>313719</v>
       </c>
       <c r="R41" t="n">
-        <v>6520664</v>
+        <v>6520649</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5065,17 +4807,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>En gammal tupp</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5102,15 +4839,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120453342</v>
+        <v>120453481</v>
       </c>
       <c r="B42" t="n">
-        <v>57364</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5118,16 +4850,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5135,20 +4867,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5158,10 +4882,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>313691</v>
+        <v>313558</v>
       </c>
       <c r="R42" t="n">
-        <v>6520712</v>
+        <v>6520816</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5194,11 +4918,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-14</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>En hane i sitt revir som hördes flera gånger som sedan landat på stambasen av en tall och började söka föda innan den skrämdes av mig.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5225,42 +4944,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120452908</v>
+        <v>120453956</v>
       </c>
       <c r="B43" t="n">
-        <v>90979</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Dialog hos validator</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>71</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5268,10 +4987,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>313704</v>
+        <v>313269</v>
       </c>
       <c r="R43" t="n">
-        <v>6520606</v>
+        <v>6520997</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5298,17 +5017,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Jag vet, att fyndet är mycket anmärkningsvärt i den delen av landet och jag själv kunde knappast tro det,för fyndet ligger utanför där jag själv och andra har rapporterad fynd för arten. Den brukar vanligen förekomma sparsam i norra Norrlands inland ner till norra Värmland. Men nu är det faktiskt så att Bohuslän/Dalsland har åtminstone i de norra delarna aldrig varit skogslösa som det påstås. I det trakter där fyndet gjorts finns faktiskt urskogsartad skog enligt definition  med en skoglig kontinuitet som sträcker sig åtminstone till 1680. Historisk källmaterial berättar om att även under den mest skogslösa tiden dvs. i mitten av 1800 talet om djup skogsbygd med timmerskogar i trakten. Faktum är att jag för två år sedan hade ytterligare ett fynd av urskogsporing i ett närbelägäget område som kyrkan ville hugga, då vågade jag inte att rapportera in för jag aldrig tidigare under nästan 30 år med skoglig naturvärdesinventering åt alla aktörer i landet varit med om liknande.</t>
+          <t>Troligen en hane men lite svår att exakt se när han flög förbi.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5317,7 +5036,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5333,6 +5051,724 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120454351</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>313488</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6520608</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Den sågs även tidigare förbifygande men nu landade den i en talltopp och kunde bättre iakttas.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120391273</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Munkedal Krokstad, Boh</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>313609</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6520729</v>
+      </c>
+      <c r="S45" t="n">
+        <v>75</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120453982</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>313285</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6520925</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>En hona och det sågs även tidigare en hona samt även en tupp i området.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120454251</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>313460</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6520664</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>En gammal tupp</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120453438</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>313613</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6520747</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ett par I sitt revir med tydligen 2 av årets ungar som än så länge toleras i reviret.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120453698</v>
+      </c>
+      <c r="B49" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hälletjärnet , Boh</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>313500</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6520930</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ett stationär par med två än så länge kvarvarande ungar</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33012-2024 artfynd.xlsx
+++ b/artfynd/A 33012-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120452908</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120389655</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120389662</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453323</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454259</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453330</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1388,6 +1423,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120389649</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120391017</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1609,6 +1654,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453310</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1714,6 +1764,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453313</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1836,6 +1891,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454351</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1954,6 +2014,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454251</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2055,6 +2120,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453531</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2161,6 +2231,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453858</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2263,6 +2338,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453391</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2365,6 +2445,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453442</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2467,6 +2552,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453447</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2569,6 +2659,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454114</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2670,6 +2765,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453996</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2771,6 +2871,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453672</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2877,6 +2982,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454233</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2978,6 +3088,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453471</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3083,6 +3198,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453364</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3184,6 +3304,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453460</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3285,6 +3410,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453528</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3386,6 +3516,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453719</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3487,6 +3622,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453731</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3588,6 +3728,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453741</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3689,6 +3834,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453763</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3790,6 +3940,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453798</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3891,6 +4046,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453987</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3992,6 +4152,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453745</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4112,6 +4277,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120391210</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4230,6 +4400,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453342</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4335,6 +4510,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453424</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4440,6 +4620,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453474</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4545,6 +4730,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453488</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4650,6 +4840,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453817</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4756,6 +4951,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454016</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4861,6 +5061,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454041</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4971,6 +5176,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454108</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5076,6 +5286,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454136</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5181,6 +5396,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453481</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5291,6 +5511,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453956</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5423,6 +5648,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120391273</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5541,6 +5771,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453982</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5655,6 +5890,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453438</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5769,8 +6009,63 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453698</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>